--- a/data/planner_colecta.xlsx
+++ b/data/planner_colecta.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sábado 10" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Viernes 9" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sábado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Viernes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47,8 +47,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,190 +419,511 @@
   </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>slot</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Francisco Bilbao con Tobalaba</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Los Leones con Eliodoro Yañez</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Tobalaba con El Bosque</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>7:00 - 8:30</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 María Belén Aragón
+📞 +56942106709
+✉️ mb.aragon@uc.cl</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Paz Atabales Pérez
+📞 +56990873432
+✉️ antonia.atabales@uc.cl
+👤 Diego Ignacio Figueroa Toro
+📞 +56982257753
+✉️ Diego.figueroatoro@estudiante.uc.cl
+👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Joaquín Hernán Tello Cortés
+📞 +56953153508
+✉️ joaquintelloc@estudiante.uc.cl</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>👤 Diego Antonio González Seguel
+📞 +56933771994
+✉️ dgonzalezseguel@gmail.com
+👤 Luis Agustin Diaz Arratia
+📞 +56976494937
+✉️ ladiaz6@uc.cl
+👤 Manuel Delpiano
+📞 +56993218991
+✉️ manuel.delpiano@uc.cl
+👤 Vicente Ignacio Araya Silva
+📞 +56945783265
+✉️ vgaraya@uc.cl</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>8:30 - 10:00</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Fernanda Godoy Araya, Krasna Ivelic</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Catalina, Sol Andrés Farías Cid</t>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Leiva Olmi
+📞 +56942555564
+✉️ antonia.leiva@uc.cl
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 María Belén Aragón
+📞 +56942106709
+✉️ mb.aragon@uc.cl</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Paz Atabales Pérez
+📞 +56990873432
+✉️ antonia.atabales@uc.cl
+👤 Diego Ignacio Figueroa Toro
+📞 +56982257753
+✉️ Diego.figueroatoro@estudiante.uc.cl
+👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Mercedes Palacios
+📞 +56990645245
+✉️ mercedes.palacios@uc.cl</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>👤 Diego Antonio González Seguel
+📞 +56933771994
+✉️ dgonzalezseguel@gmail.com
+👤 Macarena Cruz De las Heras Barros
+📞 +56968541547
+✉️ macarena.delasheras@uc.cl
+👤 Manuel Delpiano
+📞 +56993218991
+✉️ manuel.delpiano@uc.cl
+👤 Simon Valdes Menares
+📞 +56952289885
+✉️ simonvaldesmenares@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>10:00 - 11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Cony Beltran, Paz Valdivia</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Hugo Eduardo Nieto León, Krasna Ivelic, María Trinidad Fortuño</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Isidora Guiñez Maulen, Sol Andrés Farías Cid</t>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Leiva Olmi
+📞 +56942555564
+✉️ antonia.leiva@uc.cl
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 sofia monsalve
+📞 +56954561366
+✉️ sofia.monsalve@uc.cl</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>👤 Diego Ignacio Figueroa Toro
+📞 +56982257753
+✉️ Diego.figueroatoro@estudiante.uc.cl
+👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Elías Vicente Rojas Gómez
+📞 4981 3219
+✉️ elas.rojas@uc.cl
+👤 Valeria Arias Franco
+📞 +56975566067
+✉️ valeriagf@uc.cl</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>👤 Gabriela Sofía Arriagada Gallardo
+📞 +56973713863
+✉️ garriagada2005@gmail.com
+👤 Nicole Eichhorn
+📞 56979880106
+✉️ nicky@eichhorn.cl
+👤 Valentina Ignacia Gaete Moraga
+📞 +56982575538
+✉️ vggaete@uc.cl
+👤 Vanessa Castro López
+📞 +56932499866
+✉️ vanessa.castro@uc.cl</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>11:30 - 13:00</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Cony Beltran, Manuel Delpiano</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Chamo, Hugo Eduardo Nieto León</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Isidora Guiñez Maulen, Joaquin Pérez Guajardo</t>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>👤 Ignacio Matías Barros Mora
+📞 +56942488865
+✉️ ignacio.barros.mora@gmail.com
+👤 Javier Vaquero Moraga
+📞 +56934363201
+✉️ javier.vaquero@estudiante.uc.cl
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>👤 Agustina Kolubakin
+📞 +56975487974
+✉️ agustinakolubakin@gmail.com
+👤 Diego Ignacio Figueroa Toro
+📞 +56982257753
+✉️ Diego.figueroatoro@estudiante.uc.cl
+👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Felipe Beltran
+📞 +56952525679
+✉️ fbeltrang@uc.cl</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Lorca
+📞 +569 61871353
+✉️ antonia.lorca@uc.cl
+👤 Diego Max Retamal Godoy
+📞 977500440
+✉️ dretamalg@estudiante.uc.cl
+👤 Nicole Eichhorn
+📞 56979880106
+✉️ nicky@eichhorn.cl
+👤 Trinidad Diaz
+📞 +56998014657
+✉️ trinidv@estudiante.uc.cl</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>13:00 - 14:30</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Felipe Beltran, Joaquín Hernán Tello Cortés</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Francisco Eduardo Soto Sanhuezq, Jose goldenberg</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Joaquin Pérez Guajardo, Sofía Emilia Rojas Uribe</t>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>👤 Elías Felipe Carrasco Gómez
+📞 +56987580530
+✉️ e.carrasco.g@estudiante.uc.cl
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Max Burr
+📞 +56950818333
+✉️ maxburrcap@gmail.com</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>👤 Diego Ignacio Figueroa Toro
+📞 +56982257753
+✉️ Diego.figueroatoro@estudiante.uc.cl
+👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Maria Paz Oviedo Celis
+📞 +56941361760
+✉️ mzoviedo@uc.cl
+👤 Maríajosé Ignacia González Garrido
+📞 +56996327845
+✉️ mariajosegonzalez@uc.cl</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>👤 Alba Sanandres Meza
+📞 +56961230023
+✉️ albasanandres04@gmail.com
+👤 Jenmyzher Hernández García
+📞 +56959494488
+✉️ jenmyzherv@gmail.com
+👤 Rocío Márquez
+📞 +56977507902
+✉️ rociomarquez@uc.cl
+👤 Sofía Emilia Rojas Uribe
+📞 +569 9342 5594
+✉️ sofiarojasu@uc.cl</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>14:30 - 16:00</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Blanka Rolando, Felipe Beltran, Joaquín Hernán Tello Cortés</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Francisco Eduardo Soto Sanhuezq, Jose goldenberg, Magdalena mujica</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Nicolás Quintana, Seba Valenzuela, Sofía Emilia Rojas Uribe</t>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>👤 Humberto Espejo
+📞 +56956468708
+✉️ humberto.espejo@uc.cl
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 Josefa Belén Rogel Solar
+📞 +56937392290
+✉️ josefarogelsolar@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>👤 Daniel Alejandro Molleda Sánchez
+📞 +56982616264
+✉️ dmolleda@uc.cl
+👤 Diego Benjamin Vargas Muñoz
+📞 +56940177730
+✉️ dbvm2007@gmail.com
+👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Juan Agüero
+📞 +56979988568
+✉️ juan.aguero@uc.cl</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>👤 Sofía Duarte
+📞 +56993971837
+✉️ sofia.duarte@uc.cl
+👤 Sofía Emilia Rojas Uribe
+📞 +569 9342 5594
+✉️ sofiarojasu@uc.cl
+👤 Sofía Pilar Guzmán De la Sotta
+📞 +56984406013
+✉️ sofiguzdela@gmail.com
+👤 ivian colomba mardones fierro
+📞 +56933750166
+✉️ mardones.ivian@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>16:00 - 17:30</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Maite Armstrong, Nicolás Ignacio Carmona Carvajal, Vicente Correa</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Nicolás Quintana, Sofía Duarte</t>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>👤 Agustín Andrés Bustamante Alarcón
+📞 +56936747154
+✉️ agusbustam@estudiante.uc.cl
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Martín José Moyano Mozó
+📞 +56971588401
+✉️ mmoyanom@uc.cl</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>👤 Daniel Alejandro Molleda Sánchez
+📞 +56982616264
+✉️ dmolleda@uc.cl
+👤 Diego Benjamin Vargas Muñoz
+📞 +56940177730
+✉️ dbvm2007@gmail.com
+👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Francisco Eduardo Soto Sanhueza
+📞 +56940030877
+✉️ fcosoto@estudiante.uc.cl</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>👤 Blanka Rolando
+📞 +56984773281
+✉️ blankirolando@gmail.com
+👤 Farid Aponte Seminario
+📞 51479502
+✉️ fapontes@estudiante.uc.cl
+👤 Martín Andrés Sánchez Gillmore
+📞 +56996927264
+✉️ msanchezgillmore@estudiante.uc.cl
+👤 Sofía Duarte
+📞 +56993971837
+✉️ sofia.duarte@uc.cl</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>17:30 - 19:00</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Maite Armstrong, Vicente Correa</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 Jorge Vicente Pérez Villalobos
+📞 +56978844058
+✉️ jvpv@uc.cl
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Martín José Moyano Mozó
+📞 +56971588401
+✉️ mmoyanom@uc.cl</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>👤 Constanza Rojas
+📞 +56944143057
+✉️ constanza31rojas@gmail.com
+👤 Diego Benjamin Vargas Muñoz
+📞 +56940177730
+✉️ dbvm2007@gmail.com
+👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>👤 Amalia braun
+📞 +56934532687
+✉️ am.braunw@estudiante.uc.cl
+👤 Farid Aponte Seminario
+📞 51479502
+✉️ fapontes@estudiante.uc.cl
+👤 José Ignacio Vargas
+📞 +56965773295
+✉️ jivargasastu@uc.cl
+👤 Martín Andrés Sánchez Gillmore
+📞 +56996927264
+✉️ msanchezgillmore@estudiante.uc.cl</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>19:00 - 20:00</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Diego salas, Exy Máxima Garay Pereira</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>👤 Jorge Vicente Pérez Villalobos
+📞 +56978844058
+✉️ jvpv@uc.cl
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Matias Alday Flores
+📞 973835338
+✉️ malday001@gmail.com
+👤 Néstor Orlando Arispe Salinas
+📞 +56982597885
+✉️ narispe@uc.cl</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>👤 Constanza Rojas
+📞 +56944143057
+✉️ constanza31rojas@gmail.com
+👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>👤 Amalia braun
+📞 +56934532687
+✉️ am.braunw@estudiante.uc.cl
+👤 Martín Andrés Sánchez Gillmore
+📞 +56996927264
+✉️ msanchezgillmore@estudiante.uc.cl</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -614,208 +938,470 @@
   </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>slot</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Francisco Bilbao con Tobalaba</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Los Leones con Eliodoro Yañez</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Tobalaba con El Bosque</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>7:00 - 8:30</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Diego salas, Maite Armstrong</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>👤 Seba Valenzuela
+📞 +56984956696
+✉️ seba.valenzuela@uc.cl</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Krasna Ivelic
+📞 +56977086835
+✉️ krasna.ivelic@uc.cl</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>👤 Benjamin ignacio Aracena Manzo
+📞 +56933762363
+✉️ biaracena@uc.cl
+👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl
+👤 vicente gutiérrez
+📞 +56966991437
+✉️ viceg815@uc.cl</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>8:30 - 10:00</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Gabriel Osvaldo Carreño Valenzuela, Trinidad De la Maza</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>👤 Vicente Correa
+📞 +56942492216
+✉️ vicentecorrea@uc.cl</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>👤 Gabriel Osvaldo Carreño Valenzuela
+📞 +56942706127
+✉️ gabriel.carreo@estudiante.uc.cl
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Krasna Ivelic
+📞 +56977086835
+✉️ krasna.ivelic@uc.cl
+👤 Viviana Francisca Soto Rodriguez
+📞 +56972429990
+✉️ vivi.soto@uc.cl</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>👤 Dominga Fernández
+📞 +56975791343
+✉️ dominga.fernndez@uc.cl
+👤 José Manuel Oyarzún
+📞 +56961163952
+✉️ jmoyarzun@uc.cl
+👤 vicente gutiérrez
+📞 +56966991437
+✉️ viceg815@uc.cl</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>10:00 - 11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Joaquín Díaz Miranda, Max Burr</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Gabriel Osvaldo Carreño Valenzuela, Juan Antonio Moya Lagos</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Antonia Lorca, Katherina Vanessa Hoffmann Ponce, Vanessa Castro</t>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Amira Tapia Jacob
+📞 +56945449077
+✉️ Aamiratj@gmail.com
+👤 Benjamín Muñoz
+📞 +56948494689
+✉️ bmuoz@uc.cl
+👤 Joaquín Díaz
+📞 +56934227958
+✉️ jv.diaz@uc.cl
+👤 Vicente Correa
+📞 +56942492216
+✉️ vicentecorrea@uc.cl</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>👤 Gabriel Osvaldo Carreño Valenzuela
+📞 +56942706127
+✉️ gabriel.carreo@estudiante.uc.cl
+👤 Javier Alejandro Aguirre Monsalve
+📞 +56974355456
+✉️ javier.am@uc.cl
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Viviana Francisca Soto Rodriguez
+📞 +56972429990
+✉️ vivi.soto@uc.cl</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>👤 Bastián Elías Olivares Rojas
+📞 +569 30896692
+✉️ bastian.olivares@uc.cl
+👤 Magdalena
+📞 +56971645675
+✉️ maidamujica.t@gmail.com
+👤 Tomas Caillabet
+📞 +56945703738
+✉️ tecaillabet@uc.cl</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>11:30 - 13:00</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Joaquín Díaz Miranda, Max Burr</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ethiel Martina Barrientos Guerra, Macarena Cruz De las Heras</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Antonia Lorca, Natali Torres, Vanessa Castro</t>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Amira Tapia Jacob
+📞 +56945449077
+✉️ Aamiratj@gmail.com
+👤 Benjamín Muñoz
+📞 +56948494689
+✉️ bmuoz@uc.cl
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 Joaquín Díaz
+📞 +56934227958
+✉️ jv.diaz@uc.cl</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>👤 Javier Alejandro Aguirre Monsalve
+📞 +56974355456
+✉️ javier.am@uc.cl
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Juan Antonio Moya Lagos
+📞 +56958227101
+✉️ jantoniomoyal@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>👤 Bastián Elías Olivares Rojas
+📞 +569 30896692
+✉️ bastian.olivares@uc.cl
+👤 Joaquin Harrington
+📞 +56930566385
+✉️ jharrington@estudiante.uc.cl
+👤 Tomas Caillabet
+📞 +56945703738
+✉️ tecaillabet@uc.cl
+👤 Vanessa Castro Jaraba
+📞 +569 5813 9155
+✉️ vcastrr@uc.cl</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>13:00 - 14:30</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Néstor Orlando Arispe Salinas, Tomás Wittig Altmann</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Agustina Kolubakin, Bruno herrera</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Bastián Elías Olivares Rojas, Joaquin Harrington</t>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Amira Tapia Jacob
+📞 +56945449077
+✉️ Aamiratj@gmail.com
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 Trinidad
+📞 +56942188788
+✉️ trinidad.riverarios@gmail.com
+👤 Vicente Renato Serrano Martinez
+📞 36109670
+✉️ vserranom@uc.cl</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Julian Benjamin Contreras Leon
+📞 +56997774800
+✉️ juliancontrerasleon@outlook.com</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>👤 Alberto José González Rolando
+📞 +56990801639
+✉️ alberto.goro@estudiante.uc.cl
+👤 Catalina Truffello
+📞 +56966840651
+✉️ catalinatruffello@estudiante.uc.cl
+👤 Joaquin Harrington
+📞 +56930566385
+✉️ jharrington@estudiante.uc.cl</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>14:30 - 16:00</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Néstor Orlando Arispe Salinas, Simon Valdes Menares</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bruno herrera, Constanza Rojas</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Joaquin Harrington, Magdalena mujica</t>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com
+👤 Joaquín Rivas
+📞 +56954371099
+✉️ joaquinrv@uc.cl
+👤 María José Ramírez Ariztía
+📞 76094049
+✉️ mj.ramirez@estudiante.uc.cl
+👤 Trinidad
+📞 +56942188788
+✉️ trinidad.riverarios@gmail.com</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>👤 Constanza Beltran
+📞 +56974131125
+✉️ cbeltran@uc.cl
+👤 Diego Benjamin Vargas Muñoz
+📞 +56940177730
+✉️ dbvm2007@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Julian Benjamin Contreras Leon
+📞 +56997774800
+✉️ juliancontrerasleon@outlook.com</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>👤 Catalina Truffello
+📞 +56966840651
+✉️ catalinatruffello@estudiante.uc.cl
+👤 Fernanda Godoy
+📞 +56950097747
+✉️ fernigodoy26@gmail.com
+👤 Joaquín Pérez Guajardo
+📞 +56995733813
+✉️ joaquin.pg@uc.cl
+👤 Matías Miguel Ramos Segura
+📞 +56930892469
+✉️ matias.ramoss@estudiante.uc.cl</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>16:00 - 17:30</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Simon Valdes Menares, Sofía minsalve</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Constanza Rojas, Jose Ignacio Vargas</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Joaquin Harrington, Margarita Lira</t>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>👤 Alejandra Plaza
+📞 +56979781346
+✉️ alejandraplazat@gmail.com
+👤 Elisa Eugenia Reinante Gutiérrez
+📞 +56972719351
+✉️ ereinante@estudiante.uc.cl
+👤 Farid Aponte Seminario
+📞 51479502
+✉️ fapontes@estudiante.uc.cl
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>👤 Constanza Rocío Labarca Vásquez
+📞 +56944136722
+✉️ crlabarca@uc.cl
+👤 Diego Benjamin Vargas Muñoz
+📞 +56940177730
+✉️ dbvm2007@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Julian Benjamin Contreras Leon
+📞 +56997774800
+✉️ juliancontrerasleon@outlook.com</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>👤 Gimena Díaz
+📞 +56961217432
+✉️ gimediaz4@gmail.com
+👤 Matías Miguel Ramos Segura
+📞 +56930892469
+✉️ matias.ramoss@estudiante.uc.cl
+👤 Raffaella Cademartori Schmauk
+📞 +56958798788
+✉️ rcademartori@estudiante.uc.cl
+👤 Ricardo Ismael Hinojosa Cornejo
+📞 +56976020844
+✉️ ricardo.hinojosa@uc.cl</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>17:30 - 19:00</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Alejandra Plaza, Benjamin Silva</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Joaquín Rivas, Jose Ignacio Vargas</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Francisco Eduardo Soto Sanhuezq, Seba Valenzuela</t>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>👤 Benjamin Silva
+📞 +56962079086
+✉️ benjamin.silvad@uc.cl
+👤 Farid Aponte Seminario
+📞 51479502
+✉️ fapontes@estudiante.uc.cl
+👤 Ignacio Quintana Contreras
+📞 +56942021710
+✉️ ilquintana@uc.cl
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>👤 Diego Benjamin Vargas Muñoz
+📞 +56940177730
+✉️ dbvm2007@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Nicolas Manuel Ibarra Mena
+📞 +56966502797
+✉️ nibarramena3@gmail.com
+👤 Simon Valdes Menares
+📞 +56952289885
+✉️ simonvaldesmenares@gmail.com</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>👤 Macarena Cruz De las Heras Barros
+📞 +56968541547
+✉️ macarena.delasheras@uc.cl
+👤 Manuel Delpiano
+📞 +56993218991
+✉️ manuel.delpiano@uc.cl
+👤 Melanie Karina Carmona Valenzuela
+📞 +56963074267
+✉️ melanie.carmona@uc.cl</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>19:00 - 20:00</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Benjamin Silva, Vittorio Cherubini</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Agustina Kolubakin, Joaquín Rivas</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Blanka Rolando, Francisco Eduardo Soto Sanhuezq</t>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>👤 Benjamin Silva
+📞 +56962079086
+✉️ benjamin.silvad@uc.cl
+👤 Rebeca Wilson Arias
+📞 +56944892526
+✉️ rebecawilsonarias@gmail.com
+👤 Javiera Larraín
+📞 +56952945703
+✉️ javipaz.larrain@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>👤 Nicolas Manuel Ibarra Mena
+📞 +56966502797
+✉️ nibarramena3@gmail.com
+👤 Diego Benjamin Vargas Muñoz
+📞 +56940177730
+✉️ dbvm2007@gmail.com
+👤 José Tomás Nordenflycht
+📞 +56977059785
+✉️ jos.nordenflycht@uc.cl</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>👤 Vittorio Cherubini
+📞 +56996996994
+✉️ vittorio.cherubini@uc.cl
+👤 Alba Sanandres Meza
+📞 +56961230023
+✉️ albasanandres04@gmail.com
+👤 Manuel Delpiano
+📞 +56993218991
+✉️ manuel.delpiano@uc.cl</t>
         </is>
       </c>
     </row>

--- a/data/planner_colecta.xlsx
+++ b/data/planner_colecta.xlsx
@@ -456,101 +456,104 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
+          <t>👤 Diego Ignacio Figueroa Toro
+📞 56982257753
+✉️ Diego.figueroatoro@estudiante.uc.cl
+👤 José Tomás Nordenflycht
+📞 56977059785
 ✉️ jos.nordenflycht@uc.cl
 👤 María Belén Aragón
-📞 +56942106709
+📞 56942106709
 ✉️ mb.aragon@uc.cl</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
           <t>👤 Antonia Paz Atabales Pérez
-📞 +56990873432
+📞 56990873432
 ✉️ antonia.atabales@uc.cl
-👤 Diego Ignacio Figueroa Toro
-📞 +56982257753
-✉️ Diego.figueroatoro@estudiante.uc.cl
+👤 Javiera Larraín
+📞 56952945703
+✉️ javipaz.larrain@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>👤 Diego Antonio González Seguel
+📞 56933771994
+✉️ dgonzalezseguel@gmail.com
 👤 Dominga Fernández
-📞 +56975791343
+📞 56975791343
 ✉️ dominga.fernndez@uc.cl
 👤 Joaquín Hernán Tello Cortés
-📞 +56953153508
-✉️ joaquintelloc@estudiante.uc.cl</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
+📞 56953153508
+✉️ joaquintelloc@estudiante.uc.cl
+👤 Manuel Delpiano
+📞 56993218991
+✉️ manuel.delpiano@uc.cl
+👤 Vicente Ignacio Araya Silva
+📞 56945783265
+✉️ vgaraya@uc.cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>8:30 - 10:00</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Leiva Olmi
+📞 56942555564
+✉️ antonia.leiva@uc.cl
+👤 Diego Ignacio Figueroa Toro
+📞 56982257753
+✉️ Diego.figueroatoro@estudiante.uc.cl
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 María Belén Aragón
+📞 56942106709
+✉️ mb.aragon@uc.cl</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Paz Atabales Pérez
+📞 56990873432
+✉️ antonia.atabales@uc.cl
+👤 Javiera Larraín
+📞 56952945703
+✉️ javipaz.larrain@gmail.com
+👤 Macarena Cruz De las Heras Barros
+📞 56968541547
+✉️ macarena.delasheras@uc.cl
+👤 Mercedes Palacios
+📞 56990645245
+✉️ mercedes.palacios@uc.cl</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>👤 Diego Antonio González Seguel
-📞 +56933771994
+📞 56933771994
 ✉️ dgonzalezseguel@gmail.com
+👤 Dominga Fernández
+📞 56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Joaquín Hernán Tello Cortés
+📞 56953153508
+✉️ joaquintelloc@estudiante.uc.cl
 👤 Luis Agustin Diaz Arratia
-📞 +56976494937
+📞 56976494937
 ✉️ ladiaz6@uc.cl
 👤 Manuel Delpiano
-📞 +56993218991
-✉️ manuel.delpiano@uc.cl
-👤 Vicente Ignacio Araya Silva
-📞 +56945783265
-✉️ vgaraya@uc.cl</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>8:30 - 10:00</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>👤 Antonia Leiva Olmi
-📞 +56942555564
-✉️ antonia.leiva@uc.cl
-👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 María Belén Aragón
-📞 +56942106709
-✉️ mb.aragon@uc.cl</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>👤 Antonia Paz Atabales Pérez
-📞 +56990873432
-✉️ antonia.atabales@uc.cl
-👤 Diego Ignacio Figueroa Toro
-📞 +56982257753
-✉️ Diego.figueroatoro@estudiante.uc.cl
-👤 Dominga Fernández
-📞 +56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Mercedes Palacios
-📞 +56990645245
-✉️ mercedes.palacios@uc.cl</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>👤 Diego Antonio González Seguel
-📞 +56933771994
-✉️ dgonzalezseguel@gmail.com
-👤 Macarena Cruz De las Heras Barros
-📞 +56968541547
-✉️ macarena.delasheras@uc.cl
-👤 Manuel Delpiano
-📞 +56993218991
+📞 56993218991
 ✉️ manuel.delpiano@uc.cl
 👤 Simon Valdes Menares
-📞 +56952289885
+📞 56952289885
 ✉️ simonvaldesmenares@gmail.com</t>
         </is>
       </c>
@@ -564,49 +567,67 @@
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>👤 Antonia Leiva Olmi
-📞 +56942555564
+📞 56942555564
 ✉️ antonia.leiva@uc.cl
-👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
+👤 José Tomás Nordenflycht
+📞 56977059785
 ✉️ jos.nordenflycht@uc.cl
+👤 León Koehler
+📞 56942684450
+✉️ leonkoehlerm@gmail.com
+👤 Martín Sánchez Williamson
+📞 56951217559
+✉️ martinsanchezwilliamsonmic@gmail.com
+👤 Vanessa Castro López
+📞 56932499866
+✉️ vanessa.castro@uc.cl
 👤 sofia monsalve
-📞 +56954561366
+📞 56954561366
 ✉️ sofia.monsalve@uc.cl</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego Ignacio Figueroa Toro
-📞 +56982257753
-✉️ Diego.figueroatoro@estudiante.uc.cl
-👤 Dominga Fernández
-📞 +56975791343
-✉️ dominga.fernndez@uc.cl
+          <t>👤 Agustina Kolubakin
+📞 56975487974
+✉️ agustinakolubakin@gmail.com
+👤 Andrés Saab
+📞 69096909
+✉️ andresjsaab2001@gmail.com
 👤 Elías Vicente Rojas Gómez
 📞 4981 3219
 ✉️ elas.rojas@uc.cl
-👤 Valeria Arias Franco
-📞 +56975566067
-✉️ valeriagf@uc.cl</t>
+👤 Javiera Larraín
+📞 56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Pedro Cordeu
+📞 56951071233
+✉️ jpcordeu@uc.cl
+👤 Sol Andrés Farías Cid
+📞 56965096980
+✉️ sol.mfc@uc.cl</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>👤 Gabriela Sofía Arriagada Gallardo
-📞 +56973713863
+          <t>👤 Amanda Lorca Veliz
+📞 56945978313
+✉️ amanda.lorca.v@gmail.com
+👤 Antonia Lorca
+📞 +569 61871353
+✉️ antonia.lorca@uc.cl
+👤 Dominga Fernández
+📞 56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Gabriela Sofía Arriagada Gallardo
+📞 56973713863
 ✉️ garriagada2005@gmail.com
 👤 Nicole Eichhorn
 📞 56979880106
 ✉️ nicky@eichhorn.cl
-👤 Valentina Ignacia Gaete Moraga
-📞 +56982575538
-✉️ vggaete@uc.cl
-👤 Vanessa Castro López
-📞 +56932499866
-✉️ vanessa.castro@uc.cl</t>
+👤 Trinidad Diaz
+📞 56998014657
+✉️ trinidv@estudiante.uc.cl</t>
         </is>
       </c>
     </row>
@@ -618,50 +639,68 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>👤 Ignacio Matías Barros Mora
-📞 +56942488865
+          <t>👤 Elías Felipe Carrasco Gómez
+📞 56987580530
+✉️ e.carrasco.g@estudiante.uc.cl
+👤 Ignacio Matías Barros Mora
+📞 56942488865
 ✉️ ignacio.barros.mora@gmail.com
 👤 Javier Vaquero Moraga
-📞 +56934363201
+📞 56934363201
 ✉️ javier.vaquero@estudiante.uc.cl
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Martín Sánchez Williamson
+📞 56951217559
+✉️ martinsanchezwilliamsonmic@gmail.com
+👤 sofia monsalve
+📞 56954561366
+✉️ sofia.monsalve@uc.cl</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>👤 Agustina Kolubakin
+📞 56975487974
+✉️ agustinakolubakin@gmail.com
+👤 Farid Aponte Seminario
+📞 51479502
+✉️ fapontes@estudiante.uc.cl
+👤 Felipe Beltran
+📞 56952525679
+✉️ fbeltrang@uc.cl
 👤 Javiera Larraín
-📞 +56952945703
+📞 56952945703
 ✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>👤 Agustina Kolubakin
-📞 +56975487974
-✉️ agustinakolubakin@gmail.com
-👤 Diego Ignacio Figueroa Toro
-📞 +56982257753
-✉️ Diego.figueroatoro@estudiante.uc.cl
-👤 Dominga Fernández
-📞 +56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Felipe Beltran
-📞 +56952525679
-✉️ fbeltrang@uc.cl</t>
+👤 José Pedro Cordeu
+📞 56951071233
+✉️ jpcordeu@uc.cl
+👤 Paz Valdivia
+📞 +569 973362902
+✉️ pazvaldiviacorbalan@gmail.com</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>👤 Antonia Lorca
-📞 +569 61871353
-✉️ antonia.lorca@uc.cl
-👤 Diego Max Retamal Godoy
+          <t>👤 Diego Max Retamal Godoy
 📞 977500440
 ✉️ dretamalg@estudiante.uc.cl
+👤 Dominga Fernández
+📞 56975791343
+✉️ dominga.fernndez@uc.cl
 👤 Nicole Eichhorn
 📞 56979880106
 ✉️ nicky@eichhorn.cl
+👤 Sebastián Silva
+📞 56940960352
+✉️ sebasilvapino@gmail.com
 👤 Trinidad Diaz
-📞 +56998014657
-✉️ trinidv@estudiante.uc.cl</t>
+📞 56998014657
+✉️ trinidv@estudiante.uc.cl
+👤 Valeria Arias Franco
+📞 56975566067
+✉️ valeriagf@uc.cl</t>
         </is>
       </c>
     </row>
@@ -674,46 +713,64 @@
       <c r="B6" s="1" t="inlineStr">
         <is>
           <t>👤 Elías Felipe Carrasco Gómez
-📞 +56987580530
+📞 56987580530
 ✉️ e.carrasco.g@estudiante.uc.cl
+👤 Josefa Belén Rogel Solar
+📞 56937392290
+✉️ josefarogelsolar@gmail.com
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Maria Isabel Bravo
+📞 56933288880
+✉️ mbravos8@estudiante.uc.cl
+👤 Max Burr
+📞 56950818333
+✉️ maxburrcap@gmail.com
+👤 Nicolás Carmona
+📞 56975895159
+✉️ ncarmona@uc.cl</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>👤 Diego Benjamin Vargas Muñoz
+📞 56940177730
+✉️ dbvm2007@gmail.com
+👤 Farid Aponte Seminario
+📞 51479502
+✉️ fapontes@estudiante.uc.cl
+👤 Felipe Beltran
+📞 56952525679
+✉️ fbeltrang@uc.cl
 👤 Javiera Larraín
-📞 +56952945703
+📞 56952945703
 ✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Max Burr
-📞 +56950818333
-✉️ maxburrcap@gmail.com</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>👤 Diego Ignacio Figueroa Toro
-📞 +56982257753
-✉️ Diego.figueroatoro@estudiante.uc.cl
+👤 Juan Agüero
+📞 56979988568
+✉️ juan.aguero@uc.cl
+👤 Maríajosé Ignacia González Garrido
+📞 56996327845
+✉️ mariajosegonzalez@uc.cl</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>👤 Alba Sanandres Meza
+📞 56961230023
+✉️ albasanandres04@gmail.com
 👤 Dominga Fernández
-📞 +56975791343
+📞 56975791343
 ✉️ dominga.fernndez@uc.cl
 👤 Maria Paz Oviedo Celis
-📞 +56941361760
+📞 56941361760
 ✉️ mzoviedo@uc.cl
-👤 Maríajosé Ignacia González Garrido
-📞 +56996327845
-✉️ mariajosegonzalez@uc.cl</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>👤 Alba Sanandres Meza
-📞 +56961230023
-✉️ albasanandres04@gmail.com
-👤 Jenmyzher Hernández García
-📞 +56959494488
-✉️ jenmyzherv@gmail.com
 👤 Rocío Márquez
-📞 +56977507902
+📞 56977507902
 ✉️ rociomarquez@uc.cl
+👤 Sebastián Silva
+📞 56940960352
+✉️ sebasilvapino@gmail.com
 👤 Sofía Emilia Rojas Uribe
 📞 +569 9342 5594
 ✉️ sofiarojasu@uc.cl</t>
@@ -728,49 +785,67 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>👤 Humberto Espejo
-📞 +56956468708
+          <t>👤 Josefa Belén Rogel Solar
+📞 56937392290
+✉️ josefarogelsolar@gmail.com
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Martín Andrés Sánchez Gillmore
+📞 56996927264
+✉️ msanchezgillmore@estudiante.uc.cl
+👤 Max Burr
+📞 56950818333
+✉️ maxburrcap@gmail.com
+👤 Nicolás Carmona
+📞 56975895159
+✉️ ncarmona@uc.cl
+👤 Paz Arenas
+📞 56942797209
+✉️ pazarenas@icloud.com</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>👤 Daniel Alejandro Molleda Sánchez
+📞 56982616264
+✉️ dmolleda@uc.cl
+👤 Diego Benjamin Vargas Muñoz
+📞 56940177730
+✉️ dbvm2007@gmail.com
+👤 Farid Aponte Seminario
+📞 51479502
+✉️ fapontes@estudiante.uc.cl
+👤 Humberto Espejo
+📞 56956468708
 ✉️ humberto.espejo@uc.cl
 👤 Javiera Larraín
-📞 +56952945703
+📞 56952945703
 ✉️ javipaz.larrain@gmail.com
-👤 Josefa Belén Rogel Solar
-📞 +56937392290
-✉️ josefarogelsolar@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>👤 Daniel Alejandro Molleda Sánchez
-📞 +56982616264
-✉️ dmolleda@uc.cl
-👤 Diego Benjamin Vargas Muñoz
-📞 +56940177730
-✉️ dbvm2007@gmail.com
+👤 Jenmyzher Hernández García
+📞 56959494488
+✉️ jenmyzherv@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>👤 Bruno Herrera
+📞 56966622337
+✉️ bruno.herrera@uc.cl
 👤 Dominga Fernández
-📞 +56975791343
+📞 56975791343
 ✉️ dominga.fernndez@uc.cl
-👤 Juan Agüero
-📞 +56979988568
-✉️ juan.aguero@uc.cl</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>👤 Sofía Duarte
-📞 +56993971837
+👤 Sebastián Silva
+📞 56940960352
+✉️ sebasilvapino@gmail.com
+👤 Sofía Duarte
+📞 56993971837
 ✉️ sofia.duarte@uc.cl
 👤 Sofía Emilia Rojas Uribe
 📞 +569 9342 5594
 ✉️ sofiarojasu@uc.cl
-👤 Sofía Pilar Guzmán De la Sotta
-📞 +56984406013
-✉️ sofiguzdela@gmail.com
 👤 ivian colomba mardones fierro
-📞 +56933750166
+📞 56933750166
 ✉️ mardones.ivian@gmail.com</t>
         </is>
       </c>
@@ -784,49 +859,67 @@
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>👤 Agustín Andrés Bustamante Alarcón
-📞 +56936747154
+📞 56936747154
 ✉️ agusbustam@estudiante.uc.cl
-👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
+👤 Héctor Benjamín Núñez Matamala
+📞 56966955928
+✉️ hector.nm@uc.cl
+👤 José Tomás Nordenflycht
+📞 56977059785
 ✉️ jos.nordenflycht@uc.cl
-👤 Martín José Moyano Mozó
-📞 +56971588401
-✉️ mmoyanom@uc.cl</t>
+👤 Martín Andrés Sánchez Gillmore
+📞 56996927264
+✉️ msanchezgillmore@estudiante.uc.cl
+👤 Nicolás Carmona
+📞 56975895159
+✉️ ncarmona@uc.cl
+👤 Paz Arenas
+📞 56942797209
+✉️ pazarenas@icloud.com</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
           <t>👤 Daniel Alejandro Molleda Sánchez
-📞 +56982616264
+📞 56982616264
 ✉️ dmolleda@uc.cl
 👤 Diego Benjamin Vargas Muñoz
-📞 +56940177730
+📞 56940177730
 ✉️ dbvm2007@gmail.com
-👤 Dominga Fernández
-📞 +56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Francisco Eduardo Soto Sanhueza
-📞 +56940030877
-✉️ fcosoto@estudiante.uc.cl</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>👤 Blanka Rolando
-📞 +56984773281
-✉️ blankirolando@gmail.com
 👤 Farid Aponte Seminario
 📞 51479502
 ✉️ fapontes@estudiante.uc.cl
-👤 Martín Andrés Sánchez Gillmore
-📞 +56996927264
-✉️ msanchezgillmore@estudiante.uc.cl
+👤 Francisco Eduardo Soto Sanhueza
+📞 56940030877
+✉️ fcosoto@estudiante.uc.cl
+👤 Humberto Espejo
+📞 56956468708
+✉️ humberto.espejo@uc.cl
+👤 Javiera Larraín
+📞 56952945703
+✉️ javipaz.larrain@gmail.com</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>👤 Blanka Rolando
+📞 56984773281
+✉️ blankirolando@gmail.com
+👤 Bruno Herrera
+📞 56966622337
+✉️ bruno.herrera@uc.cl
+👤 Dominga Fernández
+📞 56975791343
+✉️ dominga.fernndez@uc.cl
+👤 José Ignacio Vargas
+📞 56965773295
+✉️ jivargasastu@uc.cl
 👤 Sofía Duarte
-📞 +56993971837
-✉️ sofia.duarte@uc.cl</t>
+📞 56993971837
+✉️ sofia.duarte@uc.cl
+👤 Sofía Pilar Guzmán De la Sotta
+📞 56984406013
+✉️ sofiguzdela@gmail.com</t>
         </is>
       </c>
     </row>
@@ -838,90 +931,99 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com
-👤 Jorge Vicente Pérez Villalobos
-📞 +56978844058
-✉️ jvpv@uc.cl
-👤 José Tomás Nordenflycht
-📞 +56977059785
+          <t>👤 Constanza Rojas
+📞 56944143057
+✉️ constanza31rojas@gmail.com
+👤 Héctor Benjamín Núñez Matamala
+📞 56966955928
+✉️ hector.nm@uc.cl
+👤 José Tomás Nordenflycht
+📞 56977059785
 ✉️ jos.nordenflycht@uc.cl
+👤 Martín Andrés Sánchez Gillmore
+📞 56996927264
+✉️ msanchezgillmore@estudiante.uc.cl
 👤 Martín José Moyano Mozó
-📞 +56971588401
+📞 56971588401
 ✉️ mmoyanom@uc.cl</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>👤 Constanza Rojas
-📞 +56944143057
-✉️ constanza31rojas@gmail.com
-👤 Diego Benjamin Vargas Muñoz
-📞 +56940177730
+          <t>👤 Diego Benjamin Vargas Muñoz
+📞 56940177730
 ✉️ dbvm2007@gmail.com
-👤 Dominga Fernández
-📞 +56975791343
-✉️ dominga.fernndez@uc.cl</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>👤 Amalia braun
-📞 +56934532687
-✉️ am.braunw@estudiante.uc.cl
 👤 Farid Aponte Seminario
 📞 51479502
 ✉️ fapontes@estudiante.uc.cl
+👤 Javiera Larraín
+📞 56952945703
+✉️ javipaz.larrain@gmail.com
+👤 Jorge Vicente Pérez Villalobos
+📞 56978844058
+✉️ jvpv@uc.cl</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>👤 Amalia braun
+📞 56934532687
+✉️ am.braunw@estudiante.uc.cl
+👤 Dominga Fernández
+📞 56975791343
+✉️ dominga.fernndez@uc.cl
 👤 José Ignacio Vargas
-📞 +56965773295
+📞 56965773295
 ✉️ jivargasastu@uc.cl
-👤 Martín Andrés Sánchez Gillmore
-📞 +56996927264
-✉️ msanchezgillmore@estudiante.uc.cl</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>19:00 - 20:00</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>👤 Jorge Vicente Pérez Villalobos
-📞 +56978844058
-✉️ jvpv@uc.cl
-👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl
 👤 Matias Alday Flores
 📞 973835338
 ✉️ malday001@gmail.com
+👤 Seba Valenzuela
+📞 56984956696
+✉️ seba.valenzuela@uc.cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>19:00 - 20:00</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>👤 Constanza Rojas
+📞 56944143057
+✉️ constanza31rojas@gmail.com
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Martín Andrés Sánchez Gillmore
+📞 56996927264
+✉️ msanchezgillmore@estudiante.uc.cl</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>👤 Jorge Vicente Pérez Villalobos
+📞 56978844058
+✉️ jvpv@uc.cl
 👤 Néstor Orlando Arispe Salinas
-📞 +56982597885
+📞 56982597885
 ✉️ narispe@uc.cl</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>👤 Constanza Rojas
-📞 +56944143057
-✉️ constanza31rojas@gmail.com
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>👤 Amalia braun
+📞 56934532687
+✉️ am.braunw@estudiante.uc.cl
 👤 Dominga Fernández
-📞 +56975791343
-✉️ dominga.fernndez@uc.cl</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>👤 Amalia braun
-📞 +56934532687
-✉️ am.braunw@estudiante.uc.cl
-👤 Martín Andrés Sánchez Gillmore
-📞 +56996927264
-✉️ msanchezgillmore@estudiante.uc.cl</t>
+📞 56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Matias Alday Flores
+📞 973835338
+✉️ malday001@gmail.com</t>
         </is>
       </c>
     </row>
@@ -976,30 +1078,27 @@
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>👤 Seba Valenzuela
-📞 +56984956696
+📞 56984956696
 ✉️ seba.valenzuela@uc.cl</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
           <t>👤 José Tomás Nordenflycht
-📞 +56977059785
+📞 56977059785
 ✉️ jos.nordenflycht@uc.cl
 👤 Krasna Ivelic
-📞 +56977086835
+📞 56977086835
 ✉️ krasna.ivelic@uc.cl</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>👤 Benjamin ignacio Aracena Manzo
-📞 +56933762363
+📞 56933762363
 ✉️ biaracena@uc.cl
-👤 Dominga Fernández
-📞 +56975791343
-✉️ dominga.fernndez@uc.cl
 👤 vicente gutiérrez
-📞 +56966991437
+📞 56966991437
 ✉️ viceg815@uc.cl</t>
         </is>
       </c>
@@ -1012,37 +1111,37 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>👤 Vicente Correa
-📞 +56942492216
-✉️ vicentecorrea@uc.cl</t>
+          <t>👤 Tomas Caillabet
+📞 56945703738
+✉️ tecaillabet@uc.cl</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
           <t>👤 Gabriel Osvaldo Carreño Valenzuela
-📞 +56942706127
+📞 56942706127
 ✉️ gabriel.carreo@estudiante.uc.cl
 👤 José Tomás Nordenflycht
-📞 +56977059785
+📞 56977059785
 ✉️ jos.nordenflycht@uc.cl
 👤 Krasna Ivelic
-📞 +56977086835
+📞 56977086835
 ✉️ krasna.ivelic@uc.cl
 👤 Viviana Francisca Soto Rodriguez
-📞 +56972429990
+📞 56972429990
 ✉️ vivi.soto@uc.cl</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>👤 Dominga Fernández
-📞 +56975791343
-✉️ dominga.fernndez@uc.cl
-👤 José Manuel Oyarzún
-📞 +56961163952
+          <t>👤 José Manuel Oyarzún
+📞 56961163952
 ✉️ jmoyarzun@uc.cl
+👤 Vicente Correa
+📞 56942492216
+✉️ vicentecorrea@uc.cl
 👤 vicente gutiérrez
-📞 +56966991437
+📞 56966991437
 ✉️ viceg815@uc.cl</t>
         </is>
       </c>
@@ -1054,48 +1153,45 @@
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>👤 Antonia Amira Tapia Jacob
-📞 +56945449077
-✉️ Aamiratj@gmail.com
-👤 Benjamín Muñoz
-📞 +56948494689
-✉️ bmuoz@uc.cl
-👤 Joaquín Díaz
-📞 +56934227958
-✉️ jv.diaz@uc.cl
-👤 Vicente Correa
-📞 +56942492216
-✉️ vicentecorrea@uc.cl</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>👤 Gabriel Osvaldo Carreño Valenzuela
-📞 +56942706127
-✉️ gabriel.carreo@estudiante.uc.cl
-👤 Javier Alejandro Aguirre Monsalve
-📞 +56974355456
-✉️ javier.am@uc.cl
-👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Viviana Francisca Soto Rodriguez
-📞 +56972429990
-✉️ vivi.soto@uc.cl</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>👤 Bastián Elías Olivares Rojas
 📞 +569 30896692
 ✉️ bastian.olivares@uc.cl
-👤 Magdalena
-📞 +56971645675
-✉️ maidamujica.t@gmail.com
 👤 Tomas Caillabet
-📞 +56945703738
+📞 56945703738
 ✉️ tecaillabet@uc.cl</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>👤 Gabriel Osvaldo Carreño Valenzuela
+📞 56942706127
+✉️ gabriel.carreo@estudiante.uc.cl
+👤 Javier Alejandro Aguirre Monsalve
+📞 56974355456
+✉️ javier.am@uc.cl
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Viviana Francisca Soto Rodriguez
+📞 56972429990
+✉️ vivi.soto@uc.cl</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Amira Tapia Jacob
+📞 56945449077
+✉️ Aamiratj@gmail.com
+👤 Benjamín Muñoz
+📞 56948494689
+✉️ bmuoz@uc.cl
+👤 Joaquín Díaz
+📞 56934227958
+✉️ jv.diaz@uc.cl
+👤 Vicente Correa
+📞 56942492216
+✉️ vicentecorrea@uc.cl</t>
         </is>
       </c>
     </row>
@@ -1106,45 +1202,42 @@
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>👤 Antonia Amira Tapia Jacob
-📞 +56945449077
-✉️ Aamiratj@gmail.com
-👤 Benjamín Muñoz
-📞 +56948494689
-✉️ bmuoz@uc.cl
-👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com
-👤 Joaquín Díaz
-📞 +56934227958
-✉️ jv.diaz@uc.cl</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>👤 Javier Alejandro Aguirre Monsalve
-📞 +56974355456
-✉️ javier.am@uc.cl
-👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Juan Antonio Moya Lagos
-📞 +56958227101
-✉️ jantoniomoyal@gmail.com</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>👤 Bastián Elías Olivares Rojas
 📞 +569 30896692
 ✉️ bastian.olivares@uc.cl
 👤 Joaquin Harrington
-📞 +56930566385
-✉️ jharrington@estudiante.uc.cl
-👤 Tomas Caillabet
-📞 +56945703738
-✉️ tecaillabet@uc.cl
+📞 56930566385
+✉️ jharrington@estudiante.uc.cl</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>👤 Javier Alejandro Aguirre Monsalve
+📞 56974355456
+✉️ javier.am@uc.cl
+👤 Javiera Larraín
+📞 56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Juan Antonio Moya Lagos
+📞 56958227101
+✉️ jantoniomoyal@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>👤 Antonia Amira Tapia Jacob
+📞 56945449077
+✉️ Aamiratj@gmail.com
+👤 Benjamín Muñoz
+📞 56948494689
+✉️ bmuoz@uc.cl
+👤 Joaquín Díaz
+📞 56934227958
+✉️ jv.diaz@uc.cl
 👤 Vanessa Castro Jaraba
 📞 +569 5813 9155
 ✉️ vcastrr@uc.cl</t>
@@ -1159,14 +1252,11 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>👤 Antonia Amira Tapia Jacob
-📞 +56945449077
-✉️ Aamiratj@gmail.com
-👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com
+          <t>👤 Joaquin Harrington
+📞 56930566385
+✉️ jharrington@estudiante.uc.cl
 👤 Trinidad
-📞 +56942188788
+📞 56942188788
 ✉️ trinidad.riverarios@gmail.com
 👤 Vicente Renato Serrano Martinez
 📞 36109670
@@ -1175,25 +1265,28 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl
+          <t>👤 Javiera Larraín
+📞 56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>👤 Alberto José González Rolando
+📞 56990801639
+✉️ alberto.goro@estudiante.uc.cl
+👤 Antonia Amira Tapia Jacob
+📞 56945449077
+✉️ Aamiratj@gmail.com
+👤 Catalina Truffello
+📞 56966840651
+✉️ catalinatruffello@estudiante.uc.cl
 👤 Julian Benjamin Contreras Leon
-📞 +56997774800
+📞 56997774800
 ✉️ juliancontrerasleon@outlook.com</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>👤 Alberto José González Rolando
-📞 +56990801639
-✉️ alberto.goro@estudiante.uc.cl
-👤 Catalina Truffello
-📞 +56966840651
-✉️ catalinatruffello@estudiante.uc.cl
-👤 Joaquin Harrington
-📞 +56930566385
-✉️ jharrington@estudiante.uc.cl</t>
         </is>
       </c>
     </row>
@@ -1205,49 +1298,61 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com
-👤 Joaquín Rivas
-📞 +56954371099
-✉️ joaquinrv@uc.cl
+          <t>👤 Farid Aponte Seminario
+📞 51479502
+✉️ fapontes@estudiante.uc.cl
+👤 Ignacio Quintana Contreras
+📞 56942021710
+✉️ ilquintana@uc.cl
+👤 Joaquín Pérez Guajardo
+📞 56995733813
+✉️ joaquin.pg@uc.cl
 👤 María José Ramírez Ariztía
 📞 76094049
 ✉️ mj.ramirez@estudiante.uc.cl
 👤 Trinidad
-📞 +56942188788
+📞 56942188788
 ✉️ trinidad.riverarios@gmail.com</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>👤 Constanza Beltran
-📞 +56974131125
+          <t>👤 Carlos Sebastián Catrilaf Gallegos
+📞 56936997338
+✉️ Carlos.catrilaf@uc.cl
+👤 Constanza Beltran
+📞 56974131125
 ✉️ cbeltran@uc.cl
 👤 Diego Benjamin Vargas Muñoz
-📞 +56940177730
+📞 56940177730
 ✉️ dbvm2007@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl
+👤 Fernanda Godoy
+📞 56950097747
+✉️ fernigodoy26@gmail.com
+👤 Javiera Larraín
+📞 56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>👤 Catalina Truffello
+📞 56966840651
+✉️ catalinatruffello@estudiante.uc.cl
+👤 Dominga Fernández
+📞 56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Joaquín Rivas
+📞 56954371099
+✉️ joaquinrv@uc.cl
 👤 Julian Benjamin Contreras Leon
-📞 +56997774800
-✉️ juliancontrerasleon@outlook.com</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>👤 Catalina Truffello
-📞 +56966840651
-✉️ catalinatruffello@estudiante.uc.cl
-👤 Fernanda Godoy
-📞 +56950097747
-✉️ fernigodoy26@gmail.com
-👤 Joaquín Pérez Guajardo
-📞 +56995733813
-✉️ joaquin.pg@uc.cl
+📞 56997774800
+✉️ juliancontrerasleon@outlook.com
 👤 Matías Miguel Ramos Segura
-📞 +56930892469
+📞 56930892469
 ✉️ matias.ramoss@estudiante.uc.cl</t>
         </is>
       </c>
@@ -1261,48 +1366,66 @@
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>👤 Alejandra Plaza
-📞 +56979781346
+📞 56979781346
 ✉️ alejandraplazat@gmail.com
 👤 Elisa Eugenia Reinante Gutiérrez
-📞 +56972719351
+📞 56972719351
 ✉️ ereinante@estudiante.uc.cl
 👤 Farid Aponte Seminario
 📞 51479502
 ✉️ fapontes@estudiante.uc.cl
+👤 Ignacio Quintana Contreras
+📞 56942021710
+✉️ ilquintana@uc.cl
+👤 Joaquín Pérez Guajardo
+📞 56995733813
+✉️ joaquin.pg@uc.cl
+👤 Margarita Lira
+📞 56964693026
+✉️ lmargarita@uc.cl</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>👤 Carlos Sebastián Catrilaf Gallegos
+📞 56936997338
+✉️ Carlos.catrilaf@uc.cl
+👤 Constanza Beltran
+📞 56974131125
+✉️ cbeltran@uc.cl
+👤 Diego Benjamin Vargas Muñoz
+📞 56940177730
+✉️ dbvm2007@gmail.com
+👤 Felipe Beltran
+📞 56952525679
+✉️ fbeltrang@uc.cl
 👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>👤 Constanza Rocío Labarca Vásquez
-📞 +56944136722
-✉️ crlabarca@uc.cl
-👤 Diego Benjamin Vargas Muñoz
-📞 +56940177730
-✉️ dbvm2007@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl
+📞 56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>👤 Dominga Fernández
+📞 56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Gimena Díaz
+📞 56961217432
+✉️ gimediaz4@gmail.com
+👤 Joaquín Rivas
+📞 56954371099
+✉️ joaquinrv@uc.cl
 👤 Julian Benjamin Contreras Leon
-📞 +56997774800
-✉️ juliancontrerasleon@outlook.com</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>👤 Gimena Díaz
-📞 +56961217432
-✉️ gimediaz4@gmail.com
-👤 Matías Miguel Ramos Segura
-📞 +56930892469
-✉️ matias.ramoss@estudiante.uc.cl
+📞 56997774800
+✉️ juliancontrerasleon@outlook.com
 👤 Raffaella Cademartori Schmauk
-📞 +56958798788
+📞 56958798788
 ✉️ rcademartori@estudiante.uc.cl
 👤 Ricardo Ismael Hinojosa Cornejo
-📞 +56976020844
+📞 56976020844
 ✉️ ricardo.hinojosa@uc.cl</t>
         </is>
       </c>
@@ -1316,45 +1439,51 @@
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>👤 Benjamin Silva
-📞 +56962079086
+📞 56962079086
 ✉️ benjamin.silvad@uc.cl
 👤 Farid Aponte Seminario
 📞 51479502
 ✉️ fapontes@estudiante.uc.cl
-👤 Ignacio Quintana Contreras
-📞 +56942021710
-✉️ ilquintana@uc.cl
+👤 Macarena Cruz De las Heras Barros
+📞 56968541547
+✉️ macarena.delasheras@uc.cl
+👤 Simon Valdes Menares
+📞 56952289885
+✉️ simonvaldesmenares@gmail.com
+👤 Vittorio Cherubini
+📞 56996996994
+✉️ vittorio.cherubini@uc.cl</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>👤 Diego Benjamin Vargas Muñoz
+📞 56940177730
+✉️ dbvm2007@gmail.com
 👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>👤 Diego Benjamin Vargas Muñoz
-📞 +56940177730
-✉️ dbvm2007@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
+📞 56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 56977059785
 ✉️ jos.nordenflycht@uc.cl
+👤 Manuel Delpiano
+📞 56993218991
+✉️ manuel.delpiano@uc.cl
 👤 Nicolas Manuel Ibarra Mena
-📞 +56966502797
-✉️ nibarramena3@gmail.com
-👤 Simon Valdes Menares
-📞 +56952289885
-✉️ simonvaldesmenares@gmail.com</t>
+📞 56966502797
+✉️ nibarramena3@gmail.com</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>👤 Macarena Cruz De las Heras Barros
-📞 +56968541547
-✉️ macarena.delasheras@uc.cl
-👤 Manuel Delpiano
-📞 +56993218991
-✉️ manuel.delpiano@uc.cl
+          <t>👤 Dominga Fernández
+📞 56975791343
+✉️ dominga.fernndez@uc.cl
+👤 Magdalena
+📞 56971645675
+✉️ maidamujica.t@gmail.com
 👤 Melanie Karina Carmona Valenzuela
-📞 +56963074267
+📞 56963074267
 ✉️ melanie.carmona@uc.cl</t>
         </is>
       </c>
@@ -1367,41 +1496,41 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>👤 Benjamin Silva
-📞 +56962079086
+          <t>👤 Alba Sanandres Meza
+📞 56961230023
+✉️ albasanandres04@gmail.com
+👤 Benjamin Silva
+📞 56962079086
 ✉️ benjamin.silvad@uc.cl
 👤 Rebeca Wilson Arias
-📞 +56944892526
-✉️ rebecawilsonarias@gmail.com
+📞 56944892526
+✉️ rebecawilsonarias@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>👤 Diego Benjamin Vargas Muñoz
+📞 56940177730
+✉️ dbvm2007@gmail.com
 👤 Javiera Larraín
-📞 +56952945703
-✉️ javipaz.larrain@gmail.com</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>👤 Nicolas Manuel Ibarra Mena
-📞 +56966502797
-✉️ nibarramena3@gmail.com
-👤 Diego Benjamin Vargas Muñoz
-📞 +56940177730
-✉️ dbvm2007@gmail.com
-👤 José Tomás Nordenflycht
-📞 +56977059785
-✉️ jos.nordenflycht@uc.cl</t>
+📞 56952945703
+✉️ javipaz.larrain@gmail.com
+👤 José Tomás Nordenflycht
+📞 56977059785
+✉️ jos.nordenflycht@uc.cl
+👤 Manuel Delpiano
+📞 56993218991
+✉️ manuel.delpiano@uc.cl
+👤 Nicolas Manuel Ibarra Mena
+📞 56966502797
+✉️ nibarramena3@gmail.com</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>👤 Vittorio Cherubini
-📞 +56996996994
-✉️ vittorio.cherubini@uc.cl
-👤 Alba Sanandres Meza
-📞 +56961230023
-✉️ albasanandres04@gmail.com
-👤 Manuel Delpiano
-📞 +56993218991
-✉️ manuel.delpiano@uc.cl</t>
+          <t>👤 Dominga Fernández
+📞 56975791343
+✉️ dominga.fernndez@uc.cl</t>
         </is>
       </c>
     </row>

--- a/data/planner_colecta.xlsx
+++ b/data/planner_colecta.xlsx
@@ -417,13 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,10 +440,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Holanda con Pocuro</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Los Leones con Eliodoro Yañez</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Tobalaba con El Bosque</t>
         </is>
@@ -456,44 +462,45 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego Ignacio Figueroa Toro
-📞 56982257753
-✉️ Diego.figueroatoro@estudiante.uc.cl
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 María Belén Aragón
-📞 56942106709
-✉️ mb.aragon@uc.cl</t>
+          <t>👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 mb.aragon@uc.cl
+📞 +56942106709
+✉️ María Belén Aragón</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>👤 Antonia Paz Atabales Pérez
-📞 56990873432
-✉️ antonia.atabales@uc.cl
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com</t>
+          <t>👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego Antonio González Seguel
-📞 56933771994
-✉️ dgonzalezseguel@gmail.com
-👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Joaquín Hernán Tello Cortés
-📞 56953153508
-✉️ joaquintelloc@estudiante.uc.cl
-👤 Manuel Delpiano
-📞 56993218991
-✉️ manuel.delpiano@uc.cl
-👤 Vicente Ignacio Araya Silva
-📞 56945783265
-✉️ vgaraya@uc.cl</t>
+          <t>👤 antonia.atabales@uc.cl
+📞 +56990873432
+✉️ Antonia Paz Atabales Pérez
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín
+👤 joaquintelloc@estudiante.uc.cl
+📞 +56953153508
+✉️ Joaquín Hernán Tello Cortés</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>👤 dgonzalezseguel@gmail.com
+📞 +56933771994
+✉️ Diego Antonio González Seguel
+👤 manuel.delpiano@uc.cl
+📞 +56993218991
+✉️ Manuel Delpiano
+👤 vgaraya@uc.cl
+📞 +56945783265
+✉️ Vicente Ignacio Araya Silva</t>
         </is>
       </c>
     </row>
@@ -505,56 +512,57 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>👤 Antonia Leiva Olmi
-📞 56942555564
-✉️ antonia.leiva@uc.cl
-👤 Diego Ignacio Figueroa Toro
-📞 56982257753
-✉️ Diego.figueroatoro@estudiante.uc.cl
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 María Belén Aragón
-📞 56942106709
-✉️ mb.aragon@uc.cl</t>
+          <t>👤 antonia.leiva@uc.cl
+📞 +56942555564
+✉️ Antonia Leiva Olmi
+👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 mb.aragon@uc.cl
+📞 +56942106709
+✉️ María Belén Aragón
+👤 mercedes.palacios@uc.cl
+📞 +56990645245
+✉️ Mercedes Palacios</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>👤 Antonia Paz Atabales Pérez
-📞 56990873432
-✉️ antonia.atabales@uc.cl
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 Macarena Cruz De las Heras Barros
-📞 56968541547
-✉️ macarena.delasheras@uc.cl
-👤 Mercedes Palacios
-📞 56990645245
-✉️ mercedes.palacios@uc.cl</t>
+          <t>👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 simonvaldesmenares@gmail.com
+📞 +56952289885
+✉️ Simon Valdes Menares</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego Antonio González Seguel
-📞 56933771994
-✉️ dgonzalezseguel@gmail.com
-👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Joaquín Hernán Tello Cortés
-📞 56953153508
-✉️ joaquintelloc@estudiante.uc.cl
-👤 Luis Agustin Diaz Arratia
-📞 56976494937
-✉️ ladiaz6@uc.cl
-👤 Manuel Delpiano
-📞 56993218991
-✉️ manuel.delpiano@uc.cl
-👤 Simon Valdes Menares
-📞 56952289885
-✉️ simonvaldesmenares@gmail.com</t>
+          <t>👤 antonia.atabales@uc.cl
+📞 +56990873432
+✉️ Antonia Paz Atabales Pérez
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín
+👤 joaquintelloc@estudiante.uc.cl
+📞 +56953153508
+✉️ Joaquín Hernán Tello Cortés</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>👤 dgonzalezseguel@gmail.com
+📞 +56933771994
+✉️ Diego Antonio González Seguel
+👤 ladiaz6@uc.cl
+📞 +56976494937
+✉️ Luis Agustin Diaz Arratia
+👤 macarena.delasheras@uc.cl
+📞 +56968541547
+✉️ Macarena Cruz De las Heras Barros
+👤 manuel.delpiano@uc.cl
+📞 +56993218991
+✉️ Manuel Delpiano</t>
         </is>
       </c>
     </row>
@@ -566,68 +574,78 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>👤 Antonia Leiva Olmi
-📞 56942555564
-✉️ antonia.leiva@uc.cl
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 León Koehler
-📞 56942684450
-✉️ leonkoehlerm@gmail.com
-👤 Martín Sánchez Williamson
-📞 56951217559
-✉️ martinsanchezwilliamsonmic@gmail.com
-👤 Vanessa Castro López
-📞 56932499866
-✉️ vanessa.castro@uc.cl
-👤 sofia monsalve
-📞 56954561366
-✉️ sofia.monsalve@uc.cl</t>
+          <t>👤 antonia.leiva@uc.cl
+📞 +56942555564
+✉️ Antonia Leiva Olmi
+👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 javier.duque@estudiante.uc.cl
+📞 +569 5449 9016
+✉️ Javier Duque
+👤 martinsanchezwilliamsonmic@gmail.com
+📞 +56951217559
+✉️ Martín Sánchez Williamson
+👤 sofia.monsalve@uc.cl
+📞 +56954561366
+✉️ sofia monsalve</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>👤 Agustina Kolubakin
-📞 56975487974
-✉️ agustinakolubakin@gmail.com
-👤 Andrés Saab
+          <t>👤 andresjsaab2001@gmail.com
 📞 69096909
-✉️ andresjsaab2001@gmail.com
-👤 Elías Vicente Rojas Gómez
+✉️ Andrés Saab
+👤 elas.rojas@uc.cl
 📞 4981 3219
-✉️ elas.rojas@uc.cl
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Pedro Cordeu
-📞 56951071233
-✉️ jpcordeu@uc.cl
-👤 Sol Andrés Farías Cid
-📞 56965096980
-✉️ sol.mfc@uc.cl</t>
+✉️ Elías Vicente Rojas Gómez
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 simonvaldesmenares@gmail.com
+📞 +56952289885
+✉️ Simon Valdes Menares
+👤 tfortuno@estudiante.uc.cl
+📞 +56966700631
+✉️ María Trinidad Fortuño</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>👤 Amanda Lorca Veliz
-📞 56945978313
-✉️ amanda.lorca.v@gmail.com
-👤 Antonia Lorca
-📞 +569 61871353
-✉️ antonia.lorca@uc.cl
-👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Gabriela Sofía Arriagada Gallardo
-📞 56973713863
-✉️ garriagada2005@gmail.com
-👤 Nicole Eichhorn
+          <t>👤 agustinakolubakin@gmail.com
+📞 +56975487974
+✉️ Agustina Kolubakin
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín
+👤 jpcordeu@uc.cl
+📞 +56951071233
+✉️ José Pedro Cordeu
+👤 leonkoehlerm@gmail.com
+📞 +56942684450
+✉️ León Koehler
+👤 sol.mfc@uc.cl
+📞 +56965096980
+✉️ Sol Andrés Farías Cid</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>👤 dgonzalezseguel@gmail.com
+📞 +56933771994
+✉️ Diego Antonio González Seguel
+👤 garriagada2005@gmail.com
+📞 +56973713863
+✉️ Gabriela Sofía Arriagada Gallardo
+👤 nicky@eichhorn.cl
 📞 56979880106
-✉️ nicky@eichhorn.cl
-👤 Trinidad Diaz
-📞 56998014657
-✉️ trinidv@estudiante.uc.cl</t>
+✉️ Nicole Eichhorn
+👤 vanessa.castro@uc.cl
+📞 +56932499866
+✉️ Vanessa Castro López
+👤 vggaete@uc.cl
+📞 +56982575538
+✉️ Valentina Ignacia Gaete Moraga</t>
         </is>
       </c>
     </row>
@@ -639,68 +657,78 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>👤 Elías Felipe Carrasco Gómez
-📞 56987580530
-✉️ e.carrasco.g@estudiante.uc.cl
-👤 Ignacio Matías Barros Mora
-📞 56942488865
-✉️ ignacio.barros.mora@gmail.com
-👤 Javier Vaquero Moraga
-📞 56934363201
-✉️ javier.vaquero@estudiante.uc.cl
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Martín Sánchez Williamson
-📞 56951217559
-✉️ martinsanchezwilliamsonmic@gmail.com
-👤 sofia monsalve
-📞 56954561366
-✉️ sofia.monsalve@uc.cl</t>
+          <t>👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 ignacio.barros.mora@gmail.com
+📞 +56942488865
+✉️ Ignacio Matías Barros Mora
+👤 javier.duque@estudiante.uc.cl
+📞 +569 5449 9016
+✉️ Javier Duque
+👤 javier.vaquero@estudiante.uc.cl
+📞 +56934363201
+✉️ Javier Vaquero Moraga
+👤 martinsanchezwilliamsonmic@gmail.com
+📞 +56951217559
+✉️ Martín Sánchez Williamson</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>👤 Agustina Kolubakin
-📞 56975487974
-✉️ agustinakolubakin@gmail.com
-👤 Farid Aponte Seminario
+          <t>👤 fapontes@estudiante.uc.cl
 📞 51479502
-✉️ fapontes@estudiante.uc.cl
-👤 Felipe Beltran
-📞 56952525679
-✉️ fbeltrang@uc.cl
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Pedro Cordeu
-📞 56951071233
-✉️ jpcordeu@uc.cl
-👤 Paz Valdivia
+✉️ Farid Aponte Seminario
+👤 fbeltrang@uc.cl
+📞 +56952525679
+✉️ Felipe Beltran
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 simonvaldesmenares@gmail.com
+📞 +56952289885
+✉️ Simon Valdes Menares
+👤 valeriagf@uc.cl
+📞 +56975566067
+✉️ Valeria Arias Franco</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>👤 agustinakolubakin@gmail.com
+📞 +56975487974
+✉️ Agustina Kolubakin
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín
+👤 jpcordeu@uc.cl
+📞 +56951071233
+✉️ José Pedro Cordeu
+👤 pazvaldiviacorbalan@gmail.com
 📞 +569 973362902
-✉️ pazvaldiviacorbalan@gmail.com</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>👤 Diego Max Retamal Godoy
+✉️ Paz Valdivia
+👤 sol.mfc@uc.cl
+📞 +56965096980
+✉️ Sol Andrés Farías Cid</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>👤 antonia.lorca@uc.cl
+📞 +569 61871353
+✉️ Antonia Lorca
+👤 dretamalg@estudiante.uc.cl
 📞 977500440
-✉️ dretamalg@estudiante.uc.cl
-👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Nicole Eichhorn
+✉️ Diego Max Retamal Godoy
+👤 nicky@eichhorn.cl
 📞 56979880106
-✉️ nicky@eichhorn.cl
-👤 Sebastián Silva
-📞 56940960352
-✉️ sebasilvapino@gmail.com
-👤 Trinidad Diaz
-📞 56998014657
-✉️ trinidv@estudiante.uc.cl
-👤 Valeria Arias Franco
-📞 56975566067
-✉️ valeriagf@uc.cl</t>
+✉️ Nicole Eichhorn
+👤 trinidv@estudiante.uc.cl
+📞 +56998014657
+✉️ Trinidad Diaz
+👤 vanessa.castro@uc.cl
+📞 +56932499866
+✉️ Vanessa Castro López</t>
         </is>
       </c>
     </row>
@@ -712,68 +740,78 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>👤 Elías Felipe Carrasco Gómez
-📞 56987580530
-✉️ e.carrasco.g@estudiante.uc.cl
-👤 Josefa Belén Rogel Solar
-📞 56937392290
-✉️ josefarogelsolar@gmail.com
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Maria Isabel Bravo
-📞 56933288880
-✉️ mbravos8@estudiante.uc.cl
-👤 Max Burr
-📞 56950818333
-✉️ maxburrcap@gmail.com
-👤 Nicolás Carmona
-📞 56975895159
-✉️ ncarmona@uc.cl</t>
+          <t>👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 e.carrasco.g@estudiante.uc.cl
+📞 +56987580530
+✉️ Elías Felipe Carrasco Gómez
+👤 josefarogelsolar@gmail.com
+📞 +56937392290
+✉️ Josefa Belén Rogel Solar
+👤 mbravos8@estudiante.uc.cl
+📞 +56933288880
+✉️ Maria Isabel Bravo
+👤 sebasilvapino@gmail.com
+📞 +56940960352
+✉️ Sebastián Silva</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego Benjamin Vargas Muñoz
-📞 56940177730
-✉️ dbvm2007@gmail.com
-👤 Farid Aponte Seminario
+          <t>👤 fapontes@estudiante.uc.cl
 📞 51479502
-✉️ fapontes@estudiante.uc.cl
-👤 Felipe Beltran
-📞 56952525679
-✉️ fbeltrang@uc.cl
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 Juan Agüero
-📞 56979988568
-✉️ juan.aguero@uc.cl
-👤 Maríajosé Ignacia González Garrido
-📞 56996327845
-✉️ mariajosegonzalez@uc.cl</t>
+✉️ Farid Aponte Seminario
+👤 fbeltrang@uc.cl
+📞 +56952525679
+✉️ Felipe Beltran
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 mzoviedo@uc.cl
+📞 +56941361760
+✉️ Maria Paz Oviedo Celis
+👤 ncarmona@uc.cl
+📞 +56975895159
+✉️ Nicolás Carmona</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>👤 Alba Sanandres Meza
-📞 56961230023
-✉️ albasanandres04@gmail.com
-👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Maria Paz Oviedo Celis
-📞 56941361760
-✉️ mzoviedo@uc.cl
-👤 Rocío Márquez
-📞 56977507902
-✉️ rociomarquez@uc.cl
-👤 Sebastián Silva
-📞 56940960352
-✉️ sebasilvapino@gmail.com
-👤 Sofía Emilia Rojas Uribe
+          <t>👤 Diego.figueroatoro@estudiante.uc.cl
+📞 +56982257753
+✉️ Diego Ignacio Figueroa Toro
+👤 dbvm2007@gmail.com
+📞 +56940177730
+✉️ Diego Benjamin Vargas Muñoz
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín
+👤 juan.aguero@uc.cl
+📞 +56979988568
+✉️ Juan Agüero
+👤 mariajosegonzalez@uc.cl
+📞 +56996327845
+✉️ Maríajosé Ignacia González Garrido</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>👤 albasanandres04@gmail.com
+📞 +56961230023
+✉️ Alba Sanandres Meza
+👤 jenmyzherv@gmail.com
+📞 +56959494488
+✉️ Jenmyzher Hernández García
+👤 maxburrcap@gmail.com
+📞 +56950818333
+✉️ Max Burr
+👤 rociomarquez@uc.cl
+📞 +56977507902
+✉️ Rocío Márquez
+👤 sofiarojasu@uc.cl
 📞 +569 9342 5594
-✉️ sofiarojasu@uc.cl</t>
+✉️ Sofía Emilia Rojas Uribe</t>
         </is>
       </c>
     </row>
@@ -785,68 +823,72 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>👤 Josefa Belén Rogel Solar
-📞 56937392290
-✉️ josefarogelsolar@gmail.com
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Martín Andrés Sánchez Gillmore
-📞 56996927264
-✉️ msanchezgillmore@estudiante.uc.cl
-👤 Max Burr
-📞 56950818333
-✉️ maxburrcap@gmail.com
-👤 Nicolás Carmona
-📞 56975895159
-✉️ ncarmona@uc.cl
-👤 Paz Arenas
-📞 56942797209
-✉️ pazarenas@icloud.com</t>
+          <t>👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 josefarogelsolar@gmail.com
+📞 +56937392290
+✉️ Josefa Belén Rogel Solar
+👤 msanchezgillmore@estudiante.uc.cl
+📞 +56996927264
+✉️ Martín Andrés Sánchez Gillmore
+👤 sebasilvapino@gmail.com
+📞 +56940960352
+✉️ Sebastián Silva</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>👤 Daniel Alejandro Molleda Sánchez
-📞 56982616264
-✉️ dmolleda@uc.cl
-👤 Diego Benjamin Vargas Muñoz
-📞 56940177730
-✉️ dbvm2007@gmail.com
-👤 Farid Aponte Seminario
+          <t>👤 fapontes@estudiante.uc.cl
 📞 51479502
-✉️ fapontes@estudiante.uc.cl
-👤 Humberto Espejo
-📞 56956468708
-✉️ humberto.espejo@uc.cl
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 Jenmyzher Hernández García
-📞 56959494488
-✉️ jenmyzherv@gmail.com</t>
+✉️ Farid Aponte Seminario
+👤 humberto.espejo@uc.cl
+📞 +56956468708
+✉️ Humberto Espejo
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 ncarmona@uc.cl
+📞 +56975895159
+✉️ Nicolás Carmona</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>👤 Bruno Herrera
-📞 56966622337
-✉️ bruno.herrera@uc.cl
-👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Sebastián Silva
-📞 56940960352
-✉️ sebasilvapino@gmail.com
-👤 Sofía Duarte
-📞 56993971837
-✉️ sofia.duarte@uc.cl
-👤 Sofía Emilia Rojas Uribe
+          <t>👤 Diego.figueroatoro@estudiante.uc.cl
+📞 +56982257753
+✉️ Diego Ignacio Figueroa Toro
+👤 bruno.herrera@uc.cl
+📞 +56966622337
+✉️ Bruno Herrera
+👤 dbvm2007@gmail.com
+📞 +56940177730
+✉️ Diego Benjamin Vargas Muñoz
+👤 dmolleda@uc.cl
+📞 +56982616264
+✉️ Daniel Alejandro Molleda Sánchez
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>👤 mardones.ivian@gmail.com
+📞 +56933750166
+✉️ ivian colomba mardones fierro
+👤 maxburrcap@gmail.com
+📞 +56950818333
+✉️ Max Burr
+👤 sofia.duarte@uc.cl
+📞 +56993971837
+✉️ Sofía Duarte
+👤 sofiarojasu@uc.cl
 📞 +569 9342 5594
-✉️ sofiarojasu@uc.cl
-👤 ivian colomba mardones fierro
-📞 56933750166
-✉️ mardones.ivian@gmail.com</t>
+✉️ Sofía Emilia Rojas Uribe
+👤 sofiguzdela@gmail.com
+📞 +56984406013
+✉️ Sofía Pilar Guzmán De la Sotta</t>
         </is>
       </c>
     </row>
@@ -858,68 +900,78 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>👤 Agustín Andrés Bustamante Alarcón
-📞 56936747154
-✉️ agusbustam@estudiante.uc.cl
-👤 Héctor Benjamín Núñez Matamala
-📞 56966955928
-✉️ hector.nm@uc.cl
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Martín Andrés Sánchez Gillmore
-📞 56996927264
-✉️ msanchezgillmore@estudiante.uc.cl
-👤 Nicolás Carmona
-📞 56975895159
-✉️ ncarmona@uc.cl
-👤 Paz Arenas
-📞 56942797209
-✉️ pazarenas@icloud.com</t>
+          <t>👤 agusbustam@estudiante.uc.cl
+📞 +56936747154
+✉️ Agustín Andrés Bustamante Alarcón
+👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 fcosoto@estudiante.uc.cl
+📞 +56940030877
+✉️ Francisco Eduardo Soto Sanhueza
+👤 mmoyanom@uc.cl
+📞 +56971588401
+✉️ Martín José Moyano Mozó
+👤 msanchezgillmore@estudiante.uc.cl
+📞 +56996927264
+✉️ Martín Andrés Sánchez Gillmore</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>👤 Daniel Alejandro Molleda Sánchez
-📞 56982616264
-✉️ dmolleda@uc.cl
-👤 Diego Benjamin Vargas Muñoz
-📞 56940177730
-✉️ dbvm2007@gmail.com
-👤 Farid Aponte Seminario
+          <t>👤 fapontes@estudiante.uc.cl
 📞 51479502
-✉️ fapontes@estudiante.uc.cl
-👤 Francisco Eduardo Soto Sanhueza
-📞 56940030877
-✉️ fcosoto@estudiante.uc.cl
-👤 Humberto Espejo
-📞 56956468708
-✉️ humberto.espejo@uc.cl
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com</t>
+✉️ Farid Aponte Seminario
+👤 humberto.espejo@uc.cl
+📞 +56956468708
+✉️ Humberto Espejo
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 jvpv@uc.cl
+📞 +56978844058
+✉️ Jorge Vicente Pérez Villalobos
+👤 ncarmona@uc.cl
+📞 +56975895159
+✉️ Nicolás Carmona</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>👤 Blanka Rolando
-📞 56984773281
-✉️ blankirolando@gmail.com
-👤 Bruno Herrera
-📞 56966622337
-✉️ bruno.herrera@uc.cl
-👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 José Ignacio Vargas
-📞 56965773295
-✉️ jivargasastu@uc.cl
-👤 Sofía Duarte
-📞 56993971837
-✉️ sofia.duarte@uc.cl
-👤 Sofía Pilar Guzmán De la Sotta
-📞 56984406013
-✉️ sofiguzdela@gmail.com</t>
+          <t>👤 Diego.figueroatoro@estudiante.uc.cl
+📞 +56982257753
+✉️ Diego Ignacio Figueroa Toro
+👤 bruno.herrera@uc.cl
+📞 +56966622337
+✉️ Bruno Herrera
+👤 dbvm2007@gmail.com
+📞 +56940177730
+✉️ Diego Benjamin Vargas Muñoz
+👤 dmolleda@uc.cl
+📞 +56982616264
+✉️ Daniel Alejandro Molleda Sánchez
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>👤 blankirolando@gmail.com
+📞 +56984773281
+✉️ Blanka Rolando
+👤 jivargasastu@uc.cl
+📞 +56965773295
+✉️ José Ignacio Vargas
+👤 malday001@gmail.com
+📞 973835338
+✉️ Matias Alday Flores
+👤 pazarenas@icloud.com
+📞 +56942797209
+✉️ Paz Arenas
+👤 sofia.duarte@uc.cl
+📞 +56993971837
+✉️ Sofía Duarte</t>
         </is>
       </c>
     </row>
@@ -931,56 +983,63 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>👤 Constanza Rojas
-📞 56944143057
-✉️ constanza31rojas@gmail.com
-👤 Héctor Benjamín Núñez Matamala
-📞 56966955928
-✉️ hector.nm@uc.cl
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Martín Andrés Sánchez Gillmore
-📞 56996927264
-✉️ msanchezgillmore@estudiante.uc.cl
-👤 Martín José Moyano Mozó
-📞 56971588401
-✉️ mmoyanom@uc.cl</t>
+          <t>👤 constanza31rojas@gmail.com
+📞 +56944143057
+✉️ Constanza Rojas
+👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 hector.nm@uc.cl
+📞 +56966955928
+✉️ Héctor Benjamín Núñez Matamala
+👤 mmoyanom@uc.cl
+📞 +56971588401
+✉️ Martín José Moyano Mozó
+👤 msanchezgillmore@estudiante.uc.cl
+📞 +56996927264
+✉️ Martín Andrés Sánchez Gillmore</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego Benjamin Vargas Muñoz
-📞 56940177730
-✉️ dbvm2007@gmail.com
-👤 Farid Aponte Seminario
+          <t>👤 fapontes@estudiante.uc.cl
 📞 51479502
-✉️ fapontes@estudiante.uc.cl
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 Jorge Vicente Pérez Villalobos
-📞 56978844058
-✉️ jvpv@uc.cl</t>
+✉️ Farid Aponte Seminario
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 jvpv@uc.cl
+📞 +56978844058
+✉️ Jorge Vicente Pérez Villalobos
+👤 seba.valenzuela@uc.cl
+📞 +56984956696
+✉️ Seba Valenzuela</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>👤 Amalia braun
-📞 56934532687
-✉️ am.braunw@estudiante.uc.cl
-👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 José Ignacio Vargas
-📞 56965773295
-✉️ jivargasastu@uc.cl
-👤 Matias Alday Flores
+          <t>👤 Diego.figueroatoro@estudiante.uc.cl
+📞 +56982257753
+✉️ Diego Ignacio Figueroa Toro
+👤 dbvm2007@gmail.com
+📞 +56940177730
+✉️ Diego Benjamin Vargas Muñoz
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>👤 am.braunw@estudiante.uc.cl
+📞 +56934532687
+✉️ Amalia braun
+👤 jivargasastu@uc.cl
+📞 +56965773295
+✉️ José Ignacio Vargas
+👤 malday001@gmail.com
 📞 973835338
-✉️ malday001@gmail.com
-👤 Seba Valenzuela
-📞 56984956696
-✉️ seba.valenzuela@uc.cl</t>
+✉️ Matias Alday Flores</t>
         </is>
       </c>
     </row>
@@ -992,38 +1051,42 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>👤 Constanza Rojas
-📞 56944143057
-✉️ constanza31rojas@gmail.com
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Martín Andrés Sánchez Gillmore
-📞 56996927264
-✉️ msanchezgillmore@estudiante.uc.cl</t>
+          <t>👤 constanza31rojas@gmail.com
+📞 +56944143057
+✉️ Constanza Rojas
+👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 msanchezgillmore@estudiante.uc.cl
+📞 +56996927264
+✉️ Martín Andrés Sánchez Gillmore</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>👤 Jorge Vicente Pérez Villalobos
-📞 56978844058
-✉️ jvpv@uc.cl
-👤 Néstor Orlando Arispe Salinas
-📞 56982597885
-✉️ narispe@uc.cl</t>
+          <t>👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>👤 Amalia braun
-📞 56934532687
-✉️ am.braunw@estudiante.uc.cl
-👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Matias Alday Flores
+          <t>👤 Diego.figueroatoro@estudiante.uc.cl
+📞 +56982257753
+✉️ Diego Ignacio Figueroa Toro
+👤 narispe@uc.cl
+📞 +56982597885
+✉️ Néstor Orlando Arispe Salinas</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>👤 am.braunw@estudiante.uc.cl
+📞 +56934532687
+✉️ Amalia braun
+👤 malday001@gmail.com
 📞 973835338
-✉️ malday001@gmail.com</t>
+✉️ Matias Alday Flores</t>
         </is>
       </c>
     </row>
@@ -1038,13 +1101,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,10 +1124,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Holanda con Pocuro</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Los Leones con Eliodoro Yañez</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Tobalaba con El Bosque</t>
         </is>
@@ -1077,29 +1146,33 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>👤 Seba Valenzuela
-📞 56984956696
-✉️ seba.valenzuela@uc.cl</t>
+          <t>👤 krasna.ivelic@uc.cl
+📞 +56977086835
+✉️ Krasna Ivelic</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Krasna Ivelic
-📞 56977086835
-✉️ krasna.ivelic@uc.cl</t>
+          <t>👤 viceg815@uc.cl
+📞 +56966991437
+✉️ vicente gutiérrez</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>👤 Benjamin ignacio Aracena Manzo
-📞 56933762363
-✉️ biaracena@uc.cl
-👤 vicente gutiérrez
-📞 56966991437
-✉️ viceg815@uc.cl</t>
+          <t>👤 seba.valenzuela@uc.cl
+📞 +56984956696
+✉️ Seba Valenzuela</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>👤 biaracena@uc.cl
+📞 +56933762363
+✉️ Benjamin ignacio Aracena Manzo
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht</t>
         </is>
       </c>
     </row>
@@ -1111,38 +1184,42 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>👤 Tomas Caillabet
-📞 56945703738
-✉️ tecaillabet@uc.cl</t>
+          <t>👤 krasna.ivelic@uc.cl
+📞 +56977086835
+✉️ Krasna Ivelic
+👤 vicentecorrea@uc.cl
+📞 +56942492216
+✉️ Vicente Correa</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>👤 Gabriel Osvaldo Carreño Valenzuela
-📞 56942706127
-✉️ gabriel.carreo@estudiante.uc.cl
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Krasna Ivelic
-📞 56977086835
-✉️ krasna.ivelic@uc.cl
-👤 Viviana Francisca Soto Rodriguez
-📞 56972429990
-✉️ vivi.soto@uc.cl</t>
+          <t>👤 gabriel.carreo@estudiante.uc.cl
+📞 +56942706127
+✉️ Gabriel Osvaldo Carreño Valenzuela
+👤 viceg815@uc.cl
+📞 +56966991437
+✉️ vicente gutiérrez</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>👤 José Manuel Oyarzún
-📞 56961163952
-✉️ jmoyarzun@uc.cl
-👤 Vicente Correa
-📞 56942492216
-✉️ vicentecorrea@uc.cl
-👤 vicente gutiérrez
-📞 56966991437
-✉️ viceg815@uc.cl</t>
+          <t>👤 vivi.soto@uc.cl
+📞 +56972429990
+✉️ Viviana Francisca Soto Rodriguez</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>👤 jmoyarzun@uc.cl
+📞 +56961163952
+✉️ José Manuel Oyarzún
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 tecaillabet@uc.cl
+📞 +56945703738
+✉️ Tomas Caillabet</t>
         </is>
       </c>
     </row>
@@ -1154,44 +1231,45 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>👤 Bastián Elías Olivares Rojas
-📞 +569 30896692
-✉️ bastian.olivares@uc.cl
-👤 Tomas Caillabet
-📞 56945703738
-✉️ tecaillabet@uc.cl</t>
+          <t>👤 bmuoz@uc.cl
+📞 +56948494689
+✉️ Benjamín Muñoz
+👤 vicentecorrea@uc.cl
+📞 +56942492216
+✉️ Vicente Correa</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>👤 Gabriel Osvaldo Carreño Valenzuela
-📞 56942706127
-✉️ gabriel.carreo@estudiante.uc.cl
-👤 Javier Alejandro Aguirre Monsalve
-📞 56974355456
-✉️ javier.am@uc.cl
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Viviana Francisca Soto Rodriguez
-📞 56972429990
-✉️ vivi.soto@uc.cl</t>
+          <t>👤 gabriel.carreo@estudiante.uc.cl
+📞 +56942706127
+✉️ Gabriel Osvaldo Carreño Valenzuela</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>👤 Antonia Amira Tapia Jacob
-📞 56945449077
-✉️ Aamiratj@gmail.com
-👤 Benjamín Muñoz
-📞 56948494689
-✉️ bmuoz@uc.cl
-👤 Joaquín Díaz
-📞 56934227958
-✉️ jv.diaz@uc.cl
-👤 Vicente Correa
-📞 56942492216
-✉️ vicentecorrea@uc.cl</t>
+          <t>👤 Aamiratj@gmail.com
+📞 +56945449077
+✉️ Antonia Amira Tapia Jacob
+👤 javier.am@uc.cl
+📞 +56974355456
+✉️ Javier Alejandro Aguirre Monsalve
+👤 vivi.soto@uc.cl
+📞 +56972429990
+✉️ Viviana Francisca Soto Rodriguez</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 jv.diaz@uc.cl
+📞 +56934227958
+✉️ Joaquín Díaz
+👤 tecaillabet@uc.cl
+📞 +56945703738
+✉️ Tomas Caillabet</t>
         </is>
       </c>
     </row>
@@ -1203,44 +1281,48 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>👤 Bastián Elías Olivares Rojas
+          <t>👤 bmuoz@uc.cl
+📞 +56948494689
+✉️ Benjamín Muñoz</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>👤 jantoniomoyal@gmail.com
+📞 +56958227101
+✉️ Juan Antonio Moya Lagos
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>👤 Aamiratj@gmail.com
+📞 +56945449077
+✉️ Antonia Amira Tapia Jacob
+👤 bastian.olivares@uc.cl
 📞 +569 30896692
-✉️ bastian.olivares@uc.cl
-👤 Joaquin Harrington
-📞 56930566385
-✉️ jharrington@estudiante.uc.cl</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>👤 Javier Alejandro Aguirre Monsalve
-📞 56974355456
-✉️ javier.am@uc.cl
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Juan Antonio Moya Lagos
-📞 56958227101
-✉️ jantoniomoyal@gmail.com</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>👤 Antonia Amira Tapia Jacob
-📞 56945449077
-✉️ Aamiratj@gmail.com
-👤 Benjamín Muñoz
-📞 56948494689
-✉️ bmuoz@uc.cl
-👤 Joaquín Díaz
-📞 56934227958
-✉️ jv.diaz@uc.cl
-👤 Vanessa Castro Jaraba
+✉️ Bastián Elías Olivares Rojas
+👤 javier.am@uc.cl
+📞 +56974355456
+✉️ Javier Alejandro Aguirre Monsalve</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>👤 jharrington@estudiante.uc.cl
+📞 +56930566385
+✉️ Joaquin Harrington
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 jv.diaz@uc.cl
+📞 +56934227958
+✉️ Joaquín Díaz
+👤 vcastrr@uc.cl
 📞 +569 5813 9155
-✉️ vcastrr@uc.cl</t>
+✉️ Vanessa Castro Jaraba</t>
         </is>
       </c>
     </row>
@@ -1252,41 +1334,45 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>👤 Joaquin Harrington
-📞 56930566385
-✉️ jharrington@estudiante.uc.cl
-👤 Trinidad
-📞 56942188788
-✉️ trinidad.riverarios@gmail.com
-👤 Vicente Renato Serrano Martinez
+          <t>👤 juliancontrerasleon@outlook.com
+📞 +56997774800
+✉️ Julian Benjamin Contreras Leon
+👤 trinidad.riverarios@gmail.com
+📞 +56942188788
+✉️ Trinidad
+👤 vserranom@uc.cl
 📞 36109670
-✉️ vserranom@uc.cl</t>
+✉️ Vicente Renato Serrano Martinez</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl</t>
+          <t>👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>👤 Alberto José González Rolando
-📞 56990801639
-✉️ alberto.goro@estudiante.uc.cl
-👤 Antonia Amira Tapia Jacob
-📞 56945449077
-✉️ Aamiratj@gmail.com
-👤 Catalina Truffello
-📞 56966840651
-✉️ catalinatruffello@estudiante.uc.cl
-👤 Julian Benjamin Contreras Leon
-📞 56997774800
-✉️ juliancontrerasleon@outlook.com</t>
+          <t>👤 Aamiratj@gmail.com
+📞 +56945449077
+✉️ Antonia Amira Tapia Jacob
+👤 bastian.olivares@uc.cl
+📞 +569 30896692
+✉️ Bastián Elías Olivares Rojas</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>👤 catalinatruffello@estudiante.uc.cl
+📞 +56966840651
+✉️ Catalina Truffello
+👤 jharrington@estudiante.uc.cl
+📞 +56930566385
+✉️ Joaquin Harrington
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht</t>
         </is>
       </c>
     </row>
@@ -1298,62 +1384,69 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>👤 Farid Aponte Seminario
+          <t>👤 ilquintana@uc.cl
+📞 +56942021710
+✉️ Ignacio Quintana Contreras
+👤 juliancontrerasleon@outlook.com
+📞 +56997774800
+✉️ Julian Benjamin Contreras Leon
+👤 mj.ramirez@estudiante.uc.cl
+📞 76094049
+✉️ María José Ramírez Ariztía
+👤 trinidad.riverarios@gmail.com
+📞 +56942188788
+✉️ Trinidad</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>👤 cbeltran@uc.cl
+📞 +56974131125
+✉️ Constanza Beltran
+👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 fapontes@estudiante.uc.cl
 📞 51479502
-✉️ fapontes@estudiante.uc.cl
-👤 Ignacio Quintana Contreras
-📞 56942021710
-✉️ ilquintana@uc.cl
-👤 Joaquín Pérez Guajardo
-📞 56995733813
-✉️ joaquin.pg@uc.cl
-👤 María José Ramírez Ariztía
-📞 76094049
-✉️ mj.ramirez@estudiante.uc.cl
-👤 Trinidad
-📞 56942188788
-✉️ trinidad.riverarios@gmail.com</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>👤 Carlos Sebastián Catrilaf Gallegos
-📞 56936997338
-✉️ Carlos.catrilaf@uc.cl
-👤 Constanza Beltran
-📞 56974131125
-✉️ cbeltran@uc.cl
-👤 Diego Benjamin Vargas Muñoz
-📞 56940177730
-✉️ dbvm2007@gmail.com
-👤 Fernanda Godoy
-📞 56950097747
-✉️ fernigodoy26@gmail.com
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl</t>
+✉️ Farid Aponte Seminario
+👤 fernigodoy26@gmail.com
+📞 +56950097747
+✉️ Fernanda Godoy
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>👤 Catalina Truffello
-📞 56966840651
-✉️ catalinatruffello@estudiante.uc.cl
-👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Joaquín Rivas
-📞 56954371099
-✉️ joaquinrv@uc.cl
-👤 Julian Benjamin Contreras Leon
-📞 56997774800
-✉️ juliancontrerasleon@outlook.com
-👤 Matías Miguel Ramos Segura
-📞 56930892469
-✉️ matias.ramoss@estudiante.uc.cl</t>
+          <t>👤 Carlos.catrilaf@uc.cl
+📞 +56936997338
+✉️ Carlos Sebastián Catrilaf Gallegos
+👤 dbvm2007@gmail.com
+📞 +56940177730
+✉️ Diego Benjamin Vargas Muñoz
+👤 joaquinrv@uc.cl
+📞 +56954371099
+✉️ Joaquín Rivas</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>👤 alberto.goro@estudiante.uc.cl
+📞 +56990801639
+✉️ Alberto José González Rolando
+👤 catalinatruffello@estudiante.uc.cl
+📞 +56966840651
+✉️ Catalina Truffello
+👤 joaquin.pg@uc.cl
+📞 +56995733813
+✉️ Joaquín Pérez Guajardo
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 matias.ramoss@estudiante.uc.cl
+📞 +56930892469
+✉️ Matías Miguel Ramos Segura</t>
         </is>
       </c>
     </row>
@@ -1365,68 +1458,78 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>👤 Alejandra Plaza
-📞 56979781346
-✉️ alejandraplazat@gmail.com
-👤 Elisa Eugenia Reinante Gutiérrez
-📞 56972719351
-✉️ ereinante@estudiante.uc.cl
-👤 Farid Aponte Seminario
+          <t>👤 ereinante@estudiante.uc.cl
+📞 +56972719351
+✉️ Elisa Eugenia Reinante Gutiérrez
+👤 gimediaz4@gmail.com
+📞 +56961217432
+✉️ Gimena Díaz
+👤 ilquintana@uc.cl
+📞 +56942021710
+✉️ Ignacio Quintana Contreras
+👤 juliancontrerasleon@outlook.com
+📞 +56997774800
+✉️ Julian Benjamin Contreras Leon
+👤 lmargarita@uc.cl
+📞 +56964693026
+✉️ Margarita Lira</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>👤 cbeltran@uc.cl
+📞 +56974131125
+✉️ Constanza Beltran
+👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 fapontes@estudiante.uc.cl
 📞 51479502
-✉️ fapontes@estudiante.uc.cl
-👤 Ignacio Quintana Contreras
-📞 56942021710
-✉️ ilquintana@uc.cl
-👤 Joaquín Pérez Guajardo
-📞 56995733813
-✉️ joaquin.pg@uc.cl
-👤 Margarita Lira
-📞 56964693026
-✉️ lmargarita@uc.cl</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>👤 Carlos Sebastián Catrilaf Gallegos
-📞 56936997338
-✉️ Carlos.catrilaf@uc.cl
-👤 Constanza Beltran
-📞 56974131125
-✉️ cbeltran@uc.cl
-👤 Diego Benjamin Vargas Muñoz
-📞 56940177730
-✉️ dbvm2007@gmail.com
-👤 Felipe Beltran
-📞 56952525679
-✉️ fbeltrang@uc.cl
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl</t>
+✉️ Farid Aponte Seminario
+👤 fbeltrang@uc.cl
+📞 +56952525679
+✉️ Felipe Beltran
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Gimena Díaz
-📞 56961217432
-✉️ gimediaz4@gmail.com
-👤 Joaquín Rivas
-📞 56954371099
-✉️ joaquinrv@uc.cl
-👤 Julian Benjamin Contreras Leon
-📞 56997774800
-✉️ juliancontrerasleon@outlook.com
-👤 Raffaella Cademartori Schmauk
-📞 56958798788
-✉️ rcademartori@estudiante.uc.cl
-👤 Ricardo Ismael Hinojosa Cornejo
-📞 56976020844
-✉️ ricardo.hinojosa@uc.cl</t>
+          <t>👤 Carlos.catrilaf@uc.cl
+📞 +56936997338
+✉️ Carlos Sebastián Catrilaf Gallegos
+👤 crlabarca@uc.cl
+📞 +56944136722
+✉️ Constanza Rocío Labarca Vásquez
+👤 dbvm2007@gmail.com
+📞 +56940177730
+✉️ Diego Benjamin Vargas Muñoz
+👤 joaquinrv@uc.cl
+📞 +56954371099
+✉️ Joaquín Rivas
+👤 simonvaldesmenares@gmail.com
+📞 +56952289885
+✉️ Simon Valdes Menares</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>👤 joaquin.pg@uc.cl
+📞 +56995733813
+✉️ Joaquín Pérez Guajardo
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 matias.ramoss@estudiante.uc.cl
+📞 +56930892469
+✉️ Matías Miguel Ramos Segura
+👤 rcademartori@estudiante.uc.cl
+📞 +56958798788
+✉️ Raffaella Cademartori Schmauk
+👤 ricardo.hinojosa@uc.cl
+📞 +56976020844
+✉️ Ricardo Ismael Hinojosa Cornejo</t>
         </is>
       </c>
     </row>
@@ -1438,53 +1541,57 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>👤 Benjamin Silva
-📞 56962079086
-✉️ benjamin.silvad@uc.cl
-👤 Farid Aponte Seminario
+          <t>👤 benjamin.silvad@uc.cl
+📞 +56962079086
+✉️ Benjamin Silva
+👤 manuel.delpiano@uc.cl
+📞 +56993218991
+✉️ Manuel Delpiano
+👤 vittorio.cherubini@uc.cl
+📞 +56996996994
+✉️ Vittorio Cherubini</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 fapontes@estudiante.uc.cl
 📞 51479502
-✉️ fapontes@estudiante.uc.cl
-👤 Macarena Cruz De las Heras Barros
-📞 56968541547
-✉️ macarena.delasheras@uc.cl
-👤 Simon Valdes Menares
-📞 56952289885
-✉️ simonvaldesmenares@gmail.com
-👤 Vittorio Cherubini
-📞 56996996994
-✉️ vittorio.cherubini@uc.cl</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>👤 Diego Benjamin Vargas Muñoz
-📞 56940177730
-✉️ dbvm2007@gmail.com
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Manuel Delpiano
-📞 56993218991
-✉️ manuel.delpiano@uc.cl
-👤 Nicolas Manuel Ibarra Mena
-📞 56966502797
-✉️ nibarramena3@gmail.com</t>
+✉️ Farid Aponte Seminario
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín
+👤 macarena.delasheras@uc.cl
+📞 +56968541547
+✉️ Macarena Cruz De las Heras Barros</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl
-👤 Magdalena
-📞 56971645675
-✉️ maidamujica.t@gmail.com
-👤 Melanie Karina Carmona Valenzuela
-📞 56963074267
-✉️ melanie.carmona@uc.cl</t>
+          <t>👤 dbvm2007@gmail.com
+📞 +56940177730
+✉️ Diego Benjamin Vargas Muñoz
+👤 nibarramena3@gmail.com
+📞 +56966502797
+✉️ Nicolas Manuel Ibarra Mena
+👤 simonvaldesmenares@gmail.com
+📞 +56952289885
+✉️ Simon Valdes Menares</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 maidamujica.t@gmail.com
+📞 +56971645675
+✉️ Magdalena
+👤 melanie.carmona@uc.cl
+📞 +56963074267
+✉️ Melanie Karina Carmona Valenzuela</t>
         </is>
       </c>
     </row>
@@ -1496,41 +1603,45 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>👤 Alba Sanandres Meza
-📞 56961230023
-✉️ albasanandres04@gmail.com
-👤 Benjamin Silva
-📞 56962079086
-✉️ benjamin.silvad@uc.cl
-👤 Rebeca Wilson Arias
-📞 56944892526
-✉️ rebecawilsonarias@gmail.com</t>
+          <t>👤 benjamin.silvad@uc.cl
+📞 +56962079086
+✉️ Benjamin Silva
+👤 manuel.delpiano@uc.cl
+📞 +56993218991
+✉️ Manuel Delpiano</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego Benjamin Vargas Muñoz
-📞 56940177730
-✉️ dbvm2007@gmail.com
-👤 Javiera Larraín
-📞 56952945703
-✉️ javipaz.larrain@gmail.com
-👤 José Tomás Nordenflycht
-📞 56977059785
-✉️ jos.nordenflycht@uc.cl
-👤 Manuel Delpiano
-📞 56993218991
-✉️ manuel.delpiano@uc.cl
-👤 Nicolas Manuel Ibarra Mena
-📞 56966502797
-✉️ nibarramena3@gmail.com</t>
+          <t>👤 dominga.fernndez@uc.cl
+📞 +56975791343
+✉️ Dominga Fernández
+👤 javipaz.larrain@gmail.com
+📞 +56952945703
+✉️ Javiera Larraín</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>👤 Dominga Fernández
-📞 56975791343
-✉️ dominga.fernndez@uc.cl</t>
+          <t>👤 dbvm2007@gmail.com
+📞 +56940177730
+✉️ Diego Benjamin Vargas Muñoz
+👤 nibarramena3@gmail.com
+📞 +56966502797
+✉️ Nicolas Manuel Ibarra Mena</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>👤 albasanandres04@gmail.com
+📞 +56961230023
+✉️ Alba Sanandres Meza
+👤 jos.nordenflycht@uc.cl
+📞 +56977059785
+✉️ José Tomás Nordenflycht
+👤 rebecawilsonarias@gmail.com
+📞 +56944892526
+✉️ Rebeca Wilson Arias</t>
         </is>
       </c>
     </row>

--- a/data/planner_colecta.xlsx
+++ b/data/planner_colecta.xlsx
@@ -460,49 +460,10 @@
           <t>7:00 - 8:30</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 mb.aragon@uc.cl
-📞 +56942106709
-✉️ María Belén Aragón</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>👤 antonia.atabales@uc.cl
-📞 +56990873432
-✉️ Antonia Paz Atabales Pérez
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín
-👤 joaquintelloc@estudiante.uc.cl
-📞 +56953153508
-✉️ Joaquín Hernán Tello Cortés</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>👤 dgonzalezseguel@gmail.com
-📞 +56933771994
-✉️ Diego Antonio González Seguel
-👤 manuel.delpiano@uc.cl
-📞 +56993218991
-✉️ Manuel Delpiano
-👤 vgaraya@uc.cl
-📞 +56945783265
-✉️ Vicente Ignacio Araya Silva</t>
-        </is>
-      </c>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -510,59 +471,29 @@
           <t>8:30 - 10:00</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>👤 antonia.leiva@uc.cl
-📞 +56942555564
-✉️ Antonia Leiva Olmi
-👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 mb.aragon@uc.cl
-📞 +56942106709
-✉️ María Belén Aragón
-👤 mercedes.palacios@uc.cl
-📞 +56990645245
-✉️ Mercedes Palacios</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 simonvaldesmenares@gmail.com
-📞 +56952289885
-✉️ Simon Valdes Menares</t>
-        </is>
-      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr"/>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>👤 antonia.atabales@uc.cl
-📞 +56990873432
-✉️ Antonia Paz Atabales Pérez
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín
-👤 joaquintelloc@estudiante.uc.cl
-📞 +56953153508
-✉️ Joaquín Hernán Tello Cortés</t>
+          <t>👤 Felipe Beltrán
+📞 56952525679
+✉️ fbeltrang@uc.cl
+👤 Florencia Rada
+📞 944504872
+✉️ floradasoto@gmail.com
+👤 Josefa Fernández
+📞 56991004143
+✉️ j.fernandezr@udd.cl</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>👤 dgonzalezseguel@gmail.com
-📞 +56933771994
-✉️ Diego Antonio González Seguel
-👤 ladiaz6@uc.cl
-📞 +56976494937
-✉️ Luis Agustin Diaz Arratia
-👤 macarena.delasheras@uc.cl
-📞 +56968541547
-✉️ Macarena Cruz De las Heras Barros
-👤 manuel.delpiano@uc.cl
-📞 +56993218991
-✉️ Manuel Delpiano</t>
+          <t>👤 Daniel Pino Ortiz
+📞 56969193982
+✉️ daniel.pino@uc.cl
+👤 Sebastián José Podlech Salcedo
+📞 56930810335
+✉️ sebastian.podlech@gmail.com</t>
         </is>
       </c>
     </row>
@@ -574,78 +505,42 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>👤 antonia.leiva@uc.cl
-📞 +56942555564
-✉️ Antonia Leiva Olmi
-👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 javier.duque@estudiante.uc.cl
-📞 +569 5449 9016
-✉️ Javier Duque
-👤 martinsanchezwilliamsonmic@gmail.com
-📞 +56951217559
-✉️ Martín Sánchez Williamson
-👤 sofia.monsalve@uc.cl
-📞 +56954561366
-✉️ sofia monsalve</t>
+          <t>👤 Ignacio Barros
+📞 56942488865
+✉️ ignacio.barros@uc.cl
+👤 Valentina Galleguillos
+📞 56984931263
+✉️ vgalleguillos@uc.cl</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>👤 andresjsaab2001@gmail.com
-📞 69096909
-✉️ Andrés Saab
-👤 elas.rojas@uc.cl
-📞 4981 3219
-✉️ Elías Vicente Rojas Gómez
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 simonvaldesmenares@gmail.com
-📞 +56952289885
-✉️ Simon Valdes Menares
-👤 tfortuno@estudiante.uc.cl
-📞 +56966700631
-✉️ María Trinidad Fortuño</t>
+          <t>👤 Benjamín Muñoz
+📞 56948494689
+✉️ bmuoz@uc.cl</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>👤 agustinakolubakin@gmail.com
-📞 +56975487974
-✉️ Agustina Kolubakin
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín
-👤 jpcordeu@uc.cl
-📞 +56951071233
-✉️ José Pedro Cordeu
-👤 leonkoehlerm@gmail.com
-📞 +56942684450
-✉️ León Koehler
-👤 sol.mfc@uc.cl
-📞 +56965096980
-✉️ Sol Andrés Farías Cid</t>
+          <t>👤 Felipe Beltrán
+📞 56952525679
+✉️ fbeltrang@uc.cl
+👤 Josefa Fernández
+📞 56991004143
+✉️ j.fernandezr@udd.cl
+👤 José Pedro Cordeu
+📞 56951071233
+✉️ jpcordeu@gmail.com</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>👤 dgonzalezseguel@gmail.com
-📞 +56933771994
-✉️ Diego Antonio González Seguel
-👤 garriagada2005@gmail.com
-📞 +56973713863
-✉️ Gabriela Sofía Arriagada Gallardo
-👤 nicky@eichhorn.cl
-📞 56979880106
-✉️ Nicole Eichhorn
-👤 vanessa.castro@uc.cl
-📞 +56932499866
-✉️ Vanessa Castro López
-👤 vggaete@uc.cl
-📞 +56982575538
-✉️ Valentina Ignacia Gaete Moraga</t>
+          <t>👤 Nicolás Ignacio Medina Avendaño
+📞 +56 9 5761 9298
+✉️ nicolas.medina@estudiante.uc.cl
+👤 Sebastián José Podlech Salcedo
+📞 56930810335
+✉️ sebastian.podlech@gmail.com</t>
         </is>
       </c>
     </row>
@@ -657,78 +552,51 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 ignacio.barros.mora@gmail.com
-📞 +56942488865
-✉️ Ignacio Matías Barros Mora
-👤 javier.duque@estudiante.uc.cl
-📞 +569 5449 9016
-✉️ Javier Duque
-👤 javier.vaquero@estudiante.uc.cl
-📞 +56934363201
-✉️ Javier Vaquero Moraga
-👤 martinsanchezwilliamsonmic@gmail.com
-📞 +56951217559
-✉️ Martín Sánchez Williamson</t>
+          <t>👤 Ignacio Barros
+📞 56942488865
+✉️ ignacio.barros@uc.cl
+👤 Josefa cruz
+📞 56956137573
+✉️ josefacruzlabra@gmail.com
+👤 Trinidad Gonzalez
+📞 56944622462
+✉️ trini.gonzalezespejo@gmail.com
+👤 Victoria Marshall Boehmwald
+📞 56990118895
+✉️ vmarshalb@uc.cl</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>👤 fapontes@estudiante.uc.cl
-📞 51479502
-✉️ Farid Aponte Seminario
-👤 fbeltrang@uc.cl
-📞 +56952525679
-✉️ Felipe Beltran
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 simonvaldesmenares@gmail.com
-📞 +56952289885
-✉️ Simon Valdes Menares
-👤 valeriagf@uc.cl
-📞 +56975566067
-✉️ Valeria Arias Franco</t>
+          <t>👤 Benjamín Muñoz
+📞 56948494689
+✉️ bmuoz@uc.cl
+👤 Fernanda Rojas Quezada
+📞 56932492400
+✉️ ferni.rq@gmail.com</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>👤 agustinakolubakin@gmail.com
-📞 +56975487974
-✉️ Agustina Kolubakin
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín
-👤 jpcordeu@uc.cl
-📞 +56951071233
-✉️ José Pedro Cordeu
-👤 pazvaldiviacorbalan@gmail.com
-📞 +569 973362902
-✉️ Paz Valdivia
-👤 sol.mfc@uc.cl
-📞 +56965096980
-✉️ Sol Andrés Farías Cid</t>
+          <t>👤 José Pedro Cordeu
+📞 56951071233
+✉️ jpcordeu@gmail.com
+👤 Martina Salamanca Flores
+📞 56939566835
+✉️ martina.salamanca@estudiante.uc.cl
+👤 Paz Valdivia Corbalán
+📞 56973362902
+✉️ pazvaldiviacorbalan@gmail.com</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>👤 antonia.lorca@uc.cl
-📞 +569 61871353
-✉️ Antonia Lorca
-👤 dretamalg@estudiante.uc.cl
-📞 977500440
-✉️ Diego Max Retamal Godoy
-👤 nicky@eichhorn.cl
-📞 56979880106
-✉️ Nicole Eichhorn
-👤 trinidv@estudiante.uc.cl
-📞 +56998014657
-✉️ Trinidad Diaz
-👤 vanessa.castro@uc.cl
-📞 +56932499866
-✉️ Vanessa Castro López</t>
+          <t>👤 Natalia Torres
+📞 56984482734
+✉️ nltorresg@uc.cl
+👤 Sofía Guzmán
+📞 56984406013
+✉️ sofiaguzmandls@gmail.com</t>
         </is>
       </c>
     </row>
@@ -740,78 +608,36 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 e.carrasco.g@estudiante.uc.cl
-📞 +56987580530
-✉️ Elías Felipe Carrasco Gómez
-👤 josefarogelsolar@gmail.com
-📞 +56937392290
-✉️ Josefa Belén Rogel Solar
-👤 mbravos8@estudiante.uc.cl
-📞 +56933288880
-✉️ Maria Isabel Bravo
-👤 sebasilvapino@gmail.com
-📞 +56940960352
-✉️ Sebastián Silva</t>
+          <t>👤 Maria Jose Ramirez Ariztia
+📞 56976094049
+✉️ mj.ramirez@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>👤 fapontes@estudiante.uc.cl
-📞 51479502
-✉️ Farid Aponte Seminario
-👤 fbeltrang@uc.cl
-📞 +56952525679
-✉️ Felipe Beltran
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 mzoviedo@uc.cl
-📞 +56941361760
-✉️ Maria Paz Oviedo Celis
-👤 ncarmona@uc.cl
-📞 +56975895159
-✉️ Nicolás Carmona</t>
+          <t>👤 Carolina Andrea Labra Cordero
+📞 56982052656
+✉️ carolabra@estudiante.uc.cl
+👤 Daniel Jared Huenulef Grandon
+📞 56951993174
+✉️ dhuenulefg@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego.figueroatoro@estudiante.uc.cl
-📞 +56982257753
-✉️ Diego Ignacio Figueroa Toro
-👤 dbvm2007@gmail.com
-📞 +56940177730
-✉️ Diego Benjamin Vargas Muñoz
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín
-👤 juan.aguero@uc.cl
-📞 +56979988568
-✉️ Juan Agüero
-👤 mariajosegonzalez@uc.cl
-📞 +56996327845
-✉️ Maríajosé Ignacia González Garrido</t>
+          <t>👤 Paz Valdivia Corbalán
+📞 56973362902
+✉️ pazvaldiviacorbalan@gmail.com</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>👤 albasanandres04@gmail.com
-📞 +56961230023
-✉️ Alba Sanandres Meza
-👤 jenmyzherv@gmail.com
-📞 +56959494488
-✉️ Jenmyzher Hernández García
-👤 maxburrcap@gmail.com
-📞 +56950818333
-✉️ Max Burr
-👤 rociomarquez@uc.cl
-📞 +56977507902
-✉️ Rocío Márquez
-👤 sofiarojasu@uc.cl
-📞 +569 9342 5594
-✉️ Sofía Emilia Rojas Uribe</t>
+          <t>👤 Jenmyzher Hernández
+📞 56959494488
+✉️ jenmyzherv@gmail.com
+👤 Natalia Torres
+📞 56984482734
+✉️ nltorresg@uc.cl</t>
         </is>
       </c>
     </row>
@@ -823,72 +649,33 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 josefarogelsolar@gmail.com
-📞 +56937392290
-✉️ Josefa Belén Rogel Solar
-👤 msanchezgillmore@estudiante.uc.cl
-📞 +56996927264
-✉️ Martín Andrés Sánchez Gillmore
-👤 sebasilvapino@gmail.com
-📞 +56940960352
-✉️ Sebastián Silva</t>
+          <t>👤 Constanza Rojas
+📞 56944143057
+✉️ crojas31@uc.cl</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>👤 fapontes@estudiante.uc.cl
-📞 51479502
-✉️ Farid Aponte Seminario
-👤 humberto.espejo@uc.cl
-📞 +56956468708
-✉️ Humberto Espejo
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 ncarmona@uc.cl
-📞 +56975895159
-✉️ Nicolás Carmona</t>
+          <t>👤 Carolina Andrea Labra Cordero
+📞 56982052656
+✉️ carolabra@estudiante.uc.cl
+👤 Emilia Saez
+📞 56984357201
+✉️ emilia.sez@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego.figueroatoro@estudiante.uc.cl
-📞 +56982257753
-✉️ Diego Ignacio Figueroa Toro
-👤 bruno.herrera@uc.cl
-📞 +56966622337
-✉️ Bruno Herrera
-👤 dbvm2007@gmail.com
-📞 +56940177730
-✉️ Diego Benjamin Vargas Muñoz
-👤 dmolleda@uc.cl
-📞 +56982616264
-✉️ Daniel Alejandro Molleda Sánchez
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín</t>
+          <t>👤 Elias Flip
+📞 56987580530
+✉️ e.carrasco.g@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>👤 mardones.ivian@gmail.com
-📞 +56933750166
-✉️ ivian colomba mardones fierro
-👤 maxburrcap@gmail.com
-📞 +56950818333
-✉️ Max Burr
-👤 sofia.duarte@uc.cl
-📞 +56993971837
-✉️ Sofía Duarte
-👤 sofiarojasu@uc.cl
-📞 +569 9342 5594
-✉️ Sofía Emilia Rojas Uribe
-👤 sofiguzdela@gmail.com
-📞 +56984406013
-✉️ Sofía Pilar Guzmán De la Sotta</t>
+          <t>👤 Joaquín Hernán Tello Cortés
+📞 56953153508
+✉️ joaquintelloc@estudiante.uc.cl</t>
         </is>
       </c>
     </row>
@@ -900,78 +687,45 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>👤 agusbustam@estudiante.uc.cl
-📞 +56936747154
-✉️ Agustín Andrés Bustamante Alarcón
-👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 fcosoto@estudiante.uc.cl
-📞 +56940030877
-✉️ Francisco Eduardo Soto Sanhueza
-👤 mmoyanom@uc.cl
-📞 +56971588401
-✉️ Martín José Moyano Mozó
-👤 msanchezgillmore@estudiante.uc.cl
-📞 +56996927264
-✉️ Martín Andrés Sánchez Gillmore</t>
+          <t>👤 Constanza Rojas
+📞 56944143057
+✉️ crojas31@uc.cl</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>👤 fapontes@estudiante.uc.cl
-📞 51479502
-✉️ Farid Aponte Seminario
-👤 humberto.espejo@uc.cl
-📞 +56956468708
-✉️ Humberto Espejo
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 jvpv@uc.cl
-📞 +56978844058
-✉️ Jorge Vicente Pérez Villalobos
-👤 ncarmona@uc.cl
-📞 +56975895159
-✉️ Nicolás Carmona</t>
+          <t>👤 Carolina Andrea Labra Cordero
+📞 56982052656
+✉️ carolabra@estudiante.uc.cl
+👤 Nicolás Carmona
+📞 56975895159
+✉️ ncarmona@uc.cl</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego.figueroatoro@estudiante.uc.cl
-📞 +56982257753
-✉️ Diego Ignacio Figueroa Toro
-👤 bruno.herrera@uc.cl
-📞 +56966622337
-✉️ Bruno Herrera
-👤 dbvm2007@gmail.com
-📞 +56940177730
-✉️ Diego Benjamin Vargas Muñoz
-👤 dmolleda@uc.cl
-📞 +56982616264
-✉️ Daniel Alejandro Molleda Sánchez
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín</t>
+          <t>👤 Elias Flip
+📞 56987580530
+✉️ e.carrasco.g@estudiante.uc.cl
+👤 sofia emilia rojas uribe
+📞 56993425594
+✉️ sofiarojasu@uc.cl</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>👤 blankirolando@gmail.com
-📞 +56984773281
-✉️ Blanka Rolando
-👤 jivargasastu@uc.cl
-📞 +56965773295
-✉️ José Ignacio Vargas
-👤 malday001@gmail.com
-📞 973835338
-✉️ Matias Alday Flores
-👤 pazarenas@icloud.com
-📞 +56942797209
-✉️ Paz Arenas
-👤 sofia.duarte@uc.cl
-📞 +56993971837
-✉️ Sofía Duarte</t>
+          <t>👤 Antonio Tocornal
+📞 56973756305
+✉️ antonio.tocornal@uc.cl
+👤 Joaquín Hernán Tello Cortés
+📞 56953153508
+✉️ joaquintelloc@estudiante.uc.cl
+👤 María-Jesús Labra
+📞 56982397465
+✉️ jesu.labra@estudiante.uc.cl
+👤 Nicolás Quintana
+📞 56983316396
+✉️ nicolasquintana650@gmail.com</t>
         </is>
       </c>
     </row>
@@ -983,63 +737,42 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>👤 constanza31rojas@gmail.com
-📞 +56944143057
-✉️ Constanza Rojas
-👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 hector.nm@uc.cl
-📞 +56966955928
-✉️ Héctor Benjamín Núñez Matamala
-👤 mmoyanom@uc.cl
-📞 +56971588401
-✉️ Martín José Moyano Mozó
-👤 msanchezgillmore@estudiante.uc.cl
-📞 +56996927264
-✉️ Martín Andrés Sánchez Gillmore</t>
+          <t>👤 Vittorio
+📞 56996996994
+✉️ vittorio.cherubini@uc.cl</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>👤 fapontes@estudiante.uc.cl
-📞 51479502
-✉️ Farid Aponte Seminario
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 jvpv@uc.cl
-📞 +56978844058
-✉️ Jorge Vicente Pérez Villalobos
-👤 seba.valenzuela@uc.cl
-📞 +56984956696
-✉️ Seba Valenzuela</t>
+          <t>👤 Nicolás Carmona
+📞 56975895159
+✉️ ncarmona@uc.cl
+👤 Sol Andrés Farías Cid
+📞 56965096980
+✉️ solfariascid@gmail.com</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego.figueroatoro@estudiante.uc.cl
-📞 +56982257753
-✉️ Diego Ignacio Figueroa Toro
-👤 dbvm2007@gmail.com
-📞 +56940177730
-✉️ Diego Benjamin Vargas Muñoz
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín</t>
+          <t>👤 Fernanda Godoy
+📞 950097747
+✉️ fernigodoy26@gmail.com
+👤 Nicolas Bobadilla
+📞 56968055947
+✉️ ndbobadilla@uc.cl
+👤 sofia emilia rojas uribe
+📞 56993425594
+✉️ sofiarojasu@uc.cl</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>👤 am.braunw@estudiante.uc.cl
-📞 +56934532687
-✉️ Amalia braun
-👤 jivargasastu@uc.cl
-📞 +56965773295
-✉️ José Ignacio Vargas
-👤 malday001@gmail.com
-📞 973835338
-✉️ Matias Alday Flores</t>
+          <t>👤 María-Jesús Labra
+📞 56982397465
+✉️ jesu.labra@estudiante.uc.cl
+👤 Paz Arenas
+📞 56942797209
+✉️ paz.arenas@uc.cl</t>
         </is>
       </c>
     </row>
@@ -1051,42 +784,30 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>👤 constanza31rojas@gmail.com
-📞 +56944143057
-✉️ Constanza Rojas
-👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 msanchezgillmore@estudiante.uc.cl
-📞 +56996927264
-✉️ Martín Andrés Sánchez Gillmore</t>
+          <t>👤 Vittorio
+📞 56996996994
+✉️ vittorio.cherubini@uc.cl</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht</t>
+          <t>👤 Sol Andrés Farías Cid
+📞 56965096980
+✉️ solfariascid@gmail.com</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>👤 Diego.figueroatoro@estudiante.uc.cl
-📞 +56982257753
-✉️ Diego Ignacio Figueroa Toro
-👤 narispe@uc.cl
-📞 +56982597885
-✉️ Néstor Orlando Arispe Salinas</t>
+          <t>👤 Nicolas Bobadilla
+📞 56968055947
+✉️ ndbobadilla@uc.cl</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>👤 am.braunw@estudiante.uc.cl
-📞 +56934532687
-✉️ Amalia braun
-👤 malday001@gmail.com
-📞 973835338
-✉️ Matias Alday Flores</t>
+          <t>👤 Paz Arenas
+📞 56942797209
+✉️ paz.arenas@uc.cl</t>
         </is>
       </c>
     </row>
@@ -1146,33 +867,24 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>👤 krasna.ivelic@uc.cl
-📞 +56977086835
-✉️ Krasna Ivelic</t>
+          <t>👤 Javier Vaquero Moraga
+📞 56934363201
+✉️ javier.vaquero@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>👤 viceg815@uc.cl
-📞 +56966991437
-✉️ vicente gutiérrez</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>👤 seba.valenzuela@uc.cl
-📞 +56984956696
-✉️ Seba Valenzuela</t>
-        </is>
-      </c>
+          <t>👤 Pablo Aguirre
+📞 56932584058
+✉️ paaguirrep@estudiante.uc.cl</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>👤 biaracena@uc.cl
-📞 +56933762363
-✉️ Benjamin ignacio Aracena Manzo
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht</t>
+          <t>👤 Joaquin Harrington
+📞 56930566385
+✉️ joaquinharringt@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1184,42 +896,39 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>👤 krasna.ivelic@uc.cl
-📞 +56977086835
-✉️ Krasna Ivelic
-👤 vicentecorrea@uc.cl
-📞 +56942492216
-✉️ Vicente Correa</t>
+          <t>👤 Javier Vaquero Moraga
+📞 56934363201
+✉️ javier.vaquero@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>👤 gabriel.carreo@estudiante.uc.cl
-📞 +56942706127
-✉️ Gabriel Osvaldo Carreño Valenzuela
-👤 viceg815@uc.cl
-📞 +56966991437
-✉️ vicente gutiérrez</t>
+          <t>👤 Alba
+📞 56961230023
+✉️ albasanandres04@gmail.com
+👤 Pablo Aguirre
+📞 56932584058
+✉️ paaguirrep@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>👤 vivi.soto@uc.cl
-📞 +56972429990
-✉️ Viviana Francisca Soto Rodriguez</t>
+          <t>👤 Gabriel Osvaldo Carreño Valenzuela
+📞 56942706127
+✉️ gabriel.carreo@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>👤 jmoyarzun@uc.cl
-📞 +56961163952
-✉️ José Manuel Oyarzún
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 tecaillabet@uc.cl
-📞 +56945703738
-✉️ Tomas Caillabet</t>
+          <t>👤 Joaquin Harrington
+📞 56930566385
+✉️ joaquinharringt@gmail.com
+👤 María José Sanhueza Zamora
+📞 56964963714
+✉️ msanhuezz@estudiante.uc.cl
+👤 Sofía Guzmán
+📞 56984406013
+✉️ sofiaguzmandls@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1231,45 +940,33 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>👤 bmuoz@uc.cl
-📞 +56948494689
-✉️ Benjamín Muñoz
-👤 vicentecorrea@uc.cl
-📞 +56942492216
-✉️ Vicente Correa</t>
+          <t>👤 Vicente Correa
+📞 56942492216
+✉️ vicentecorrea@uc.cl</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>👤 gabriel.carreo@estudiante.uc.cl
-📞 +56942706127
-✉️ Gabriel Osvaldo Carreño Valenzuela</t>
+          <t>👤 Alba
+📞 56961230023
+✉️ albasanandres04@gmail.com</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>👤 Aamiratj@gmail.com
-📞 +56945449077
-✉️ Antonia Amira Tapia Jacob
-👤 javier.am@uc.cl
-📞 +56974355456
-✉️ Javier Alejandro Aguirre Monsalve
-👤 vivi.soto@uc.cl
-📞 +56972429990
-✉️ Viviana Francisca Soto Rodriguez</t>
+          <t>👤 Gabriela Sofía Lafuente Kuncar
+📞 941338248
+✉️ gabrielalafuentek@gmail.com
+👤 Pía Belén González González
+📞 56984055514
+✉️ piabgz@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 jv.diaz@uc.cl
-📞 +56934227958
-✉️ Joaquín Díaz
-👤 tecaillabet@uc.cl
-📞 +56945703738
-✉️ Tomas Caillabet</t>
+          <t>👤 Trinidad Diaz
+📞 56998014657
+✉️ trinidv@estudiante.uc.cl</t>
         </is>
       </c>
     </row>
@@ -1281,48 +978,36 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>👤 bmuoz@uc.cl
-📞 +56948494689
-✉️ Benjamín Muñoz</t>
+          <t>👤 Vicente Correa
+📞 56942492216
+✉️ vicentecorrea@uc.cl
+👤 Vicente Serrano
+📞 +56 936109670
+✉️ vicente.serrano2006@gmail.com</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>👤 jantoniomoyal@gmail.com
-📞 +56958227101
-✉️ Juan Antonio Moya Lagos
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín</t>
+          <t>👤 Agustina Kolubakin
+📞 56975487974
+✉️ agustinakolubakin@gmail.com</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>👤 Aamiratj@gmail.com
-📞 +56945449077
-✉️ Antonia Amira Tapia Jacob
-👤 bastian.olivares@uc.cl
-📞 +569 30896692
-✉️ Bastián Elías Olivares Rojas
-👤 javier.am@uc.cl
-📞 +56974355456
-✉️ Javier Alejandro Aguirre Monsalve</t>
+          <t>👤 Gregory Maximiliano Williamson Molina
+📞 56966324146
+✉️ gregorywilliamson@estudiante.uc.cl
+👤 Waldo Alberto Seguel Salazar
+📞 56973351525
+✉️ waldo.seguel@uc.cl</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>👤 jharrington@estudiante.uc.cl
-📞 +56930566385
-✉️ Joaquin Harrington
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 jv.diaz@uc.cl
-📞 +56934227958
-✉️ Joaquín Díaz
-👤 vcastrr@uc.cl
-📞 +569 5813 9155
-✉️ Vanessa Castro Jaraba</t>
+          <t>👤 Trinidad Diaz
+📞 56998014657
+✉️ trinidv@estudiante.uc.cl</t>
         </is>
       </c>
     </row>
@@ -1334,45 +1019,33 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>👤 juliancontrerasleon@outlook.com
-📞 +56997774800
-✉️ Julian Benjamin Contreras Leon
-👤 trinidad.riverarios@gmail.com
-📞 +56942188788
-✉️ Trinidad
-👤 vserranom@uc.cl
-📞 36109670
-✉️ Vicente Renato Serrano Martinez</t>
+          <t>👤 Vicente Serrano
+📞 +56 936109670
+✉️ vicente.serrano2006@gmail.com</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín</t>
+          <t>👤 Agustina Kolubakin
+📞 56975487974
+✉️ agustinakolubakin@gmail.com</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>👤 Aamiratj@gmail.com
-📞 +56945449077
-✉️ Antonia Amira Tapia Jacob
-👤 bastian.olivares@uc.cl
-📞 +569 30896692
-✉️ Bastián Elías Olivares Rojas</t>
+          <t>👤 Alicia Castro Claps
+📞 56944188084
+✉️ alicastroclaps@gmail.com
+👤 Josefina Roman
+📞 56942945530
+✉️ joseroman.a@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>👤 catalinatruffello@estudiante.uc.cl
-📞 +56966840651
-✉️ Catalina Truffello
-👤 jharrington@estudiante.uc.cl
-📞 +56930566385
-✉️ Joaquin Harrington
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht</t>
+          <t>👤 Blanka Rolando
+📞 56984773281
+✉️ blankirolando@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1384,69 +1057,48 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>👤 ilquintana@uc.cl
-📞 +56942021710
-✉️ Ignacio Quintana Contreras
-👤 juliancontrerasleon@outlook.com
-📞 +56997774800
-✉️ Julian Benjamin Contreras Leon
-👤 mj.ramirez@estudiante.uc.cl
-📞 76094049
-✉️ María José Ramírez Ariztía
-👤 trinidad.riverarios@gmail.com
-📞 +56942188788
-✉️ Trinidad</t>
+          <t>👤 Consuelo Isidora Carrillo Prado
+📞 944056421
+✉️ carrillo.consuelo.ip@gmail.com
+👤 Magdalena Andrade Rodriguez
+📞 56931910429
+✉️ maneandrade@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>👤 cbeltran@uc.cl
-📞 +56974131125
-✉️ Constanza Beltran
-👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 fapontes@estudiante.uc.cl
-📞 51479502
-✉️ Farid Aponte Seminario
-👤 fernigodoy26@gmail.com
-📞 +56950097747
-✉️ Fernanda Godoy
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín</t>
+          <t>👤 Joaquin Rivas
+📞 56954371099
+✉️ joaquinrv@uc.cl</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>👤 Carlos.catrilaf@uc.cl
-📞 +56936997338
-✉️ Carlos Sebastián Catrilaf Gallegos
-👤 dbvm2007@gmail.com
-📞 +56940177730
-✉️ Diego Benjamin Vargas Muñoz
-👤 joaquinrv@uc.cl
-📞 +56954371099
-✉️ Joaquín Rivas</t>
+          <t>👤 Alicia Castro Claps
+📞 56944188084
+✉️ alicastroclaps@gmail.com
+👤 Josefina Roman
+📞 56942945530
+✉️ joseroman.a@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>👤 alberto.goro@estudiante.uc.cl
-📞 +56990801639
-✉️ Alberto José González Rolando
-👤 catalinatruffello@estudiante.uc.cl
-📞 +56966840651
-✉️ Catalina Truffello
-👤 joaquin.pg@uc.cl
-📞 +56995733813
-✉️ Joaquín Pérez Guajardo
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 matias.ramoss@estudiante.uc.cl
-📞 +56930892469
-✉️ Matías Miguel Ramos Segura</t>
+          <t>👤 Antonia Lorca
+📞 56961871353
+✉️ antonia.lorca.velizz@gmail.com
+👤 Antonia Tapia
+📞 +569 4544 9077
+✉️ atapij@estudiante.uc.cl
+👤 Bastian Olivares
+📞 56930896692
+✉️ bastian.olivares@uc.cl
+👤 Luna Villarroel Assis
+📞 56992946894
+✉️ lunavillarroel@estudiante.uc.cl
+👤 Sofia Gutierrez
+📞 56939171497
+✉️ sofiiagutierrezg@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1458,78 +1110,39 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>👤 ereinante@estudiante.uc.cl
-📞 +56972719351
-✉️ Elisa Eugenia Reinante Gutiérrez
-👤 gimediaz4@gmail.com
-📞 +56961217432
-✉️ Gimena Díaz
-👤 ilquintana@uc.cl
-📞 +56942021710
-✉️ Ignacio Quintana Contreras
-👤 juliancontrerasleon@outlook.com
-📞 +56997774800
-✉️ Julian Benjamin Contreras Leon
-👤 lmargarita@uc.cl
-📞 +56964693026
-✉️ Margarita Lira</t>
+          <t>👤 Jacinta Ortiz santander
+📞 56944061259
+✉️ jacinta.ortiz@uc.cl</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>👤 cbeltran@uc.cl
-📞 +56974131125
-✉️ Constanza Beltran
-👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 fapontes@estudiante.uc.cl
-📞 51479502
-✉️ Farid Aponte Seminario
-👤 fbeltrang@uc.cl
-📞 +56952525679
-✉️ Felipe Beltran
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín</t>
+          <t>👤 Catalina Truffello
+📞 56966840651
+✉️ catruya@gmail.com
+👤 Joaquin Rivas
+📞 56954371099
+✉️ joaquinrv@uc.cl</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>👤 Carlos.catrilaf@uc.cl
-📞 +56936997338
-✉️ Carlos Sebastián Catrilaf Gallegos
-👤 crlabarca@uc.cl
-📞 +56944136722
-✉️ Constanza Rocío Labarca Vásquez
-👤 dbvm2007@gmail.com
-📞 +56940177730
-✉️ Diego Benjamin Vargas Muñoz
-👤 joaquinrv@uc.cl
-📞 +56954371099
-✉️ Joaquín Rivas
-👤 simonvaldesmenares@gmail.com
-📞 +56952289885
-✉️ Simon Valdes Menares</t>
+          <t>👤 Alicia Castro Claps
+📞 56944188084
+✉️ alicastroclaps@gmail.com
+👤 Sofía Diez Leyton
+📞 56996765617
+✉️ sofi.leyton.ch@estudiante.uc.cl</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>👤 joaquin.pg@uc.cl
-📞 +56995733813
-✉️ Joaquín Pérez Guajardo
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 matias.ramoss@estudiante.uc.cl
-📞 +56930892469
-✉️ Matías Miguel Ramos Segura
-👤 rcademartori@estudiante.uc.cl
-📞 +56958798788
-✉️ Raffaella Cademartori Schmauk
-👤 ricardo.hinojosa@uc.cl
-📞 +56976020844
-✉️ Ricardo Ismael Hinojosa Cornejo</t>
+          <t>👤 Antonia Tapia
+📞 +569 4544 9077
+✉️ atapij@estudiante.uc.cl
+👤 Bastian Olivares
+📞 56930896692
+✉️ bastian.olivares@uc.cl</t>
         </is>
       </c>
     </row>
@@ -1541,57 +1154,27 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>👤 benjamin.silvad@uc.cl
-📞 +56962079086
-✉️ Benjamin Silva
-👤 manuel.delpiano@uc.cl
-📞 +56993218991
-✉️ Manuel Delpiano
-👤 vittorio.cherubini@uc.cl
-📞 +56996996994
-✉️ Vittorio Cherubini</t>
+          <t>👤 Jacinta Ortiz santander
+📞 56944061259
+✉️ jacinta.ortiz@uc.cl</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 fapontes@estudiante.uc.cl
-📞 51479502
-✉️ Farid Aponte Seminario
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín
-👤 macarena.delasheras@uc.cl
-📞 +56968541547
-✉️ Macarena Cruz De las Heras Barros</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>👤 dbvm2007@gmail.com
-📞 +56940177730
-✉️ Diego Benjamin Vargas Muñoz
-👤 nibarramena3@gmail.com
-📞 +56966502797
-✉️ Nicolas Manuel Ibarra Mena
-👤 simonvaldesmenares@gmail.com
-📞 +56952289885
-✉️ Simon Valdes Menares</t>
-        </is>
-      </c>
+          <t>👤 Catalina Truffello
+📞 56966840651
+✉️ catruya@gmail.com</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 maidamujica.t@gmail.com
-📞 +56971645675
-✉️ Magdalena
-👤 melanie.carmona@uc.cl
-📞 +56963074267
-✉️ Melanie Karina Carmona Valenzuela</t>
+          <t>👤 Sebastián Silva
+📞 56940960352
+✉️ sebasilvapino@gmail.com
+👤 Teresita Schwarzenberg Velásquez
+📞 56957659950
+✉️ teresitaschve@gmail.com</t>
         </is>
       </c>
     </row>
@@ -1601,49 +1184,22 @@
           <t>19:00 - 20:00</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>👤 benjamin.silvad@uc.cl
-📞 +56962079086
-✉️ Benjamin Silva
-👤 manuel.delpiano@uc.cl
-📞 +56993218991
-✉️ Manuel Delpiano</t>
-        </is>
-      </c>
+      <c r="B10" s="1" t="inlineStr"/>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>👤 dominga.fernndez@uc.cl
-📞 +56975791343
-✉️ Dominga Fernández
-👤 javipaz.larrain@gmail.com
-📞 +56952945703
-✉️ Javiera Larraín</t>
+          <t>👤 Catalina Truffello
+📞 56966840651
+✉️ catruya@gmail.com</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>👤 dbvm2007@gmail.com
-📞 +56940177730
-✉️ Diego Benjamin Vargas Muñoz
-👤 nibarramena3@gmail.com
-📞 +56966502797
-✉️ Nicolas Manuel Ibarra Mena</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>👤 albasanandres04@gmail.com
-📞 +56961230023
-✉️ Alba Sanandres Meza
-👤 jos.nordenflycht@uc.cl
-📞 +56977059785
-✉️ José Tomás Nordenflycht
-👤 rebecawilsonarias@gmail.com
-📞 +56944892526
-✉️ Rebeca Wilson Arias</t>
-        </is>
-      </c>
+          <t>👤 Fernanda Godoy
+📞 950097747
+✉️ fernigodoy26@gmail.com</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
